--- a/AR_overdue_zoho.xlsx
+++ b/AR_overdue_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:O88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 01/09/2026</t>
+As of 09/09/2026</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>333</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>293</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>277</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>277</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>246</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>246</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>246</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>215</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>215</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>215</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>212</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>212</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>175</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>156</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>156</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>156</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>156</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>126</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>126</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>126</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>126</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>126</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5150,7 +5150,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>510492000001460089</t>
+          <t>510492000001359025</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5188,17 +5188,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>242075</t>
+          <t>242012</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>510492000000639001</t>
+          <t>510492000000317525</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>De'Osa Engineering Services</t>
+          <t>EAGLE PROPERTY CARE</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="N68" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="O68" t="n">
         <v>1.0</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>510492000001460115</t>
+          <t>510492000001460089</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5257,17 +5257,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>242076</t>
+          <t>242075</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>510492000001460106</t>
+          <t>510492000000639001</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>MOUNTAINS OF GLORY</t>
+          <t>De'Osa Engineering Services</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>250.0</v>
+        <v>120.0</v>
       </c>
       <c r="N69" t="n">
-        <v>250.0</v>
+        <v>120.0</v>
       </c>
       <c r="O69" t="n">
         <v>1.0</v>
@@ -5288,74 +5288,1247 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>510492000001460115</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>242076</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>510492000001460106</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>MOUNTAINS OF GLORY</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>250.0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>250.0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
         <is>
           <t>510492000001460138</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>242077</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>510492000000386033</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>ALPHA EUROPE LTD</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>510492000001474010</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>242080</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>510492000001474001</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>First Class Learning Reading Central</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>270.0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>270.0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>510492000001477103</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>242081</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>510492000000541229</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Optimum Global Care</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>510492000001482001</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H70" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>242077</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>510492000000386033</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>ALPHA EUROPE LTD</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M70" t="n">
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>242082</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>510492000001057001</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Corby Motors Ltd</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>555.0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>555.0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>510492000001482018</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>242083</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>510492000001413024</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>88 DRIVING SCHOOL LTD</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>110.0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>110.0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>510492000001488015</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>242084</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>510492000001488006</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>SPOT CLEANERS LTD</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>130.0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>130.0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>510492000001367115</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>242017</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>510492000001025001</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>310.3</v>
+      </c>
+      <c r="N77" t="n">
+        <v>310.3</v>
+      </c>
+      <c r="O77" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>510492000001486010</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>242085</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>510492000000122647</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="N78" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>510492000001486042</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>242087</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>510492000000123247</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>NOMADS CLOTHING LIMITED</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="N79" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>510492000001486058</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>242088</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>510492000000123277</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Patrick Shoes Limited</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>477.6</v>
+      </c>
+      <c r="N80" t="n">
+        <v>477.6</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>510492000001486075</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>242089</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>510492000000192073</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>SUPERHOUSE (UK) LIMITED</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="N81" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>510492000001486171</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>242095</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>510492000000505059</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Chorus Music Therapy &amp; Education</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>510492000001486235</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>242099</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>510492000000742001</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Adam’s Painting and Decorating</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
         <v>240.0</v>
       </c>
-      <c r="N70" t="n">
+      <c r="N83" t="n">
         <v>240.0</v>
       </c>
-      <c r="O70" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="55" t="inlineStr">
+      <c r="O83" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>510492000001486347</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>242106</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>510492000000123277</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Patrick Shoes Limited</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>510492000001496082</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>242113</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>510492000001155001</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Galloway Pest Control</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>360.0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>360.0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>510492000001496003</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>242112</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>510492000000822033</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Sofiya Designs Limited</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>420.0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>420.0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>510492000001496109</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>242114</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>510492000001378001</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>270.0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>270.0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5364,7 +6537,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A71:O71"/>
+    <mergeCell ref="A88:O88"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_overdue_zoho.xlsx
+++ b/AR_overdue_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O88"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>510492000001001139</t>
+          <t>510492000001001241</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1182,21 +1182,21 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>241789</t>
+          <t>241792</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000362001</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>DRC AUTO SALES LTD</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N10" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O10" t="n">
         <v>1.0</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>510492000001001241</t>
+          <t>510492000001001309</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1255,17 +1255,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>241792</t>
+          <t>241794</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>510492000000362001</t>
+          <t>510492000000475183</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>DRC AUTO SALES LTD</t>
+          <t>Usman Autos and Services</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>240.0</v>
+        <v>150.0</v>
       </c>
       <c r="N11" t="n">
-        <v>240.0</v>
+        <v>150.0</v>
       </c>
       <c r="O11" t="n">
         <v>1.0</v>
@@ -1286,7 +1286,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>510492000001001309</t>
+          <t>510492000001023019</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1306,12 +1306,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>212</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1324,17 +1324,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>241794</t>
+          <t>241807</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>510492000000475183</t>
+          <t>510492000001023001</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Usman Autos and Services</t>
+          <t>IZEC PRESTIGE CARS LTD</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>150.0</v>
+        <v>300.0</v>
       </c>
       <c r="N12" t="n">
-        <v>150.0</v>
+        <v>300.0</v>
       </c>
       <c r="O12" t="n">
         <v>1.0</v>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>510492000001023019</t>
+          <t>510492000001023057</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>241807</t>
+          <t>241808</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>510492000001023001</t>
+          <t>510492000000792001</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>IZEC PRESTIGE CARS LTD</t>
+          <t>Edens Edge Limited</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>300.0</v>
+        <v>360.0</v>
       </c>
       <c r="N13" t="n">
-        <v>300.0</v>
+        <v>360.0</v>
       </c>
       <c r="O13" t="n">
         <v>1.0</v>
@@ -1424,7 +1424,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>510492000001023057</t>
+          <t>510492000001059100</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1444,12 +1444,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>241808</t>
+          <t>241824</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>510492000000792001</t>
+          <t>510492000000703337</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Edens Edge Limited</t>
+          <t>Golden Dollar Ltd</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>360.0</v>
+        <v>230.0</v>
       </c>
       <c r="N14" t="n">
-        <v>360.0</v>
+        <v>230.0</v>
       </c>
       <c r="O14" t="n">
         <v>1.0</v>
@@ -1493,7 +1493,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>510492000001059051</t>
+          <t>510492000001079019</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1513,12 +1513,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1531,17 +1531,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>241823</t>
+          <t>241828</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000001079001</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>RBD Driving School</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>375.0</v>
+        <v>200.0</v>
       </c>
       <c r="N15" t="n">
-        <v>395.0</v>
+        <v>200.0</v>
       </c>
       <c r="O15" t="n">
         <v>1.0</v>
@@ -1562,7 +1562,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>510492000001059100</t>
+          <t>510492000001093173</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1600,17 +1600,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>241824</t>
+          <t>241836</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>510492000000703337</t>
+          <t>510492000000240001</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Golden Dollar Ltd</t>
+          <t>Cameraboss Photography</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>230.0</v>
+        <v>200.0</v>
       </c>
       <c r="N16" t="n">
-        <v>230.0</v>
+        <v>200.0</v>
       </c>
       <c r="O16" t="n">
         <v>1.0</v>
@@ -1631,7 +1631,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>510492000001079019</t>
+          <t>510492000001093241</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>241828</t>
+          <t>241838</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>510492000001079001</t>
+          <t>510492000000362001</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>RBD Driving School</t>
+          <t>DRC AUTO SALES LTD</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>200.0</v>
+        <v>240.0</v>
       </c>
       <c r="N17" t="n">
-        <v>200.0</v>
+        <v>240.0</v>
       </c>
       <c r="O17" t="n">
         <v>1.0</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>510492000001093139</t>
+          <t>510492000001093411</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1720,12 +1720,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1734,21 +1734,21 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>241835</t>
+          <t>241843</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000327139</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>BATHROOMS LONDON LIMITED</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1757,10 +1757,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>238.8</v>
+        <v>180.0</v>
       </c>
       <c r="N18" t="n">
-        <v>238.8</v>
+        <v>360.0</v>
       </c>
       <c r="O18" t="n">
         <v>1.0</v>
@@ -1769,7 +1769,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>510492000001093173</t>
+          <t>510492000001105001</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1807,17 +1807,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>241836</t>
+          <t>241852</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>510492000000240001</t>
+          <t>510492000000327139</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Cameraboss Photography</t>
+          <t>BATHROOMS LONDON LIMITED</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>200.0</v>
+        <v>126.6</v>
       </c>
       <c r="N19" t="n">
-        <v>200.0</v>
+        <v>126.6</v>
       </c>
       <c r="O19" t="n">
         <v>1.0</v>
@@ -1838,7 +1838,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>510492000001093241</t>
+          <t>510492000001105107</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1858,12 +1858,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1876,17 +1876,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>241838</t>
+          <t>241855</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>510492000000362001</t>
+          <t>510492000001023001</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>DRC AUTO SALES LTD</t>
+          <t>IZEC PRESTIGE CARS LTD</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>240.0</v>
+        <v>28.8</v>
       </c>
       <c r="N20" t="n">
-        <v>240.0</v>
+        <v>28.8</v>
       </c>
       <c r="O20" t="n">
         <v>1.0</v>
@@ -1907,7 +1907,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>510492000001093411</t>
+          <t>510492000001105141</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1945,17 +1945,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>241843</t>
+          <t>241856</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>510492000000327139</t>
+          <t>510492000000703337</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>BATHROOMS LONDON LIMITED</t>
+          <t>Golden Dollar Ltd</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>180.0</v>
+        <v>54.83</v>
       </c>
       <c r="N21" t="n">
-        <v>360.0</v>
+        <v>54.83</v>
       </c>
       <c r="O21" t="n">
         <v>1.0</v>
@@ -1976,7 +1976,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>510492000001105001</t>
+          <t>510492000001141001</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2014,17 +2014,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>241852</t>
+          <t>241868</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>510492000000327139</t>
+          <t>510492000001135181</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>BATHROOMS LONDON LIMITED</t>
+          <t>Greyson Studios</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>126.6</v>
+        <v>150.0</v>
       </c>
       <c r="N22" t="n">
-        <v>126.6</v>
+        <v>150.0</v>
       </c>
       <c r="O22" t="n">
         <v>1.0</v>
@@ -2045,7 +2045,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>510492000001105107</t>
+          <t>510492000001144294</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>175</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2083,17 +2083,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>241855</t>
+          <t>241869</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>510492000001023001</t>
+          <t>510492000001144276</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>IZEC PRESTIGE CARS LTD</t>
+          <t>Creativa Ltd</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>28.8</v>
+        <v>240.0</v>
       </c>
       <c r="N23" t="n">
-        <v>28.8</v>
+        <v>240.0</v>
       </c>
       <c r="O23" t="n">
         <v>1.0</v>
@@ -2114,7 +2114,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>510492000001105141</t>
+          <t>510492000001180143</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>156</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>241856</t>
+          <t>241878</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>510492000000703337</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Golden Dollar Ltd</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>54.83</v>
+        <v>238.8</v>
       </c>
       <c r="N24" t="n">
-        <v>54.83</v>
+        <v>238.8</v>
       </c>
       <c r="O24" t="n">
         <v>1.0</v>
@@ -2183,7 +2183,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>510492000001111409</t>
+          <t>510492000001180178</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>156</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2221,17 +2221,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>241858</t>
+          <t>241879</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000000240001</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Cameraboss Photography</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>240.0</v>
+        <v>200.0</v>
       </c>
       <c r="N25" t="n">
-        <v>240.0</v>
+        <v>200.0</v>
       </c>
       <c r="O25" t="n">
         <v>1.0</v>
@@ -2252,7 +2252,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>510492000001141001</t>
+          <t>510492000001180423</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2272,12 +2272,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2290,17 +2290,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>241868</t>
+          <t>241886</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>510492000001135181</t>
+          <t>510492000000327139</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Greyson Studios</t>
+          <t>BATHROOMS LONDON LIMITED</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>150.0</v>
+        <v>360.0</v>
       </c>
       <c r="N26" t="n">
-        <v>150.0</v>
+        <v>360.0</v>
       </c>
       <c r="O26" t="n">
         <v>1.0</v>
@@ -2321,7 +2321,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>510492000001144294</t>
+          <t>510492000001180633</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>156</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2359,17 +2359,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>241869</t>
+          <t>241892</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>510492000001144276</t>
+          <t>510492000000792001</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Creativa Ltd</t>
+          <t>Edens Edge Limited</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>510492000001180143</t>
+          <t>510492000001231066</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>126</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>241878</t>
+          <t>241914</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>510492000001180178</t>
+          <t>510492000001231082</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>126</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>241879</t>
+          <t>241915</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2528,7 +2528,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>510492000001180423</t>
+          <t>510492000001231194</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>241886</t>
+          <t>241922</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2597,7 +2597,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>510492000001180528</t>
+          <t>510492000001231242</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>126</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>241889</t>
+          <t>241925</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2666,7 +2666,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>510492000001180633</t>
+          <t>510492000001231370</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2686,12 +2686,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>126</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2704,17 +2704,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>241892</t>
+          <t>241933</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>510492000000792001</t>
+          <t>510492000001079001</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Edens Edge Limited</t>
+          <t>RBD Driving School</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>240.0</v>
+        <v>200.0</v>
       </c>
       <c r="N32" t="n">
-        <v>240.0</v>
+        <v>200.0</v>
       </c>
       <c r="O32" t="n">
         <v>1.0</v>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>510492000001231066</t>
+          <t>510492000001231386</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2769,21 +2769,21 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>241914</t>
+          <t>241934</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000001144276</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>Creativa Ltd</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N33" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O33" t="n">
         <v>1.0</v>
@@ -2804,7 +2804,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>510492000001231082</t>
+          <t>510492000001279033</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>241915</t>
+          <t>241949</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>510492000000240001</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Cameraboss Photography</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>200.0</v>
+        <v>216.4</v>
       </c>
       <c r="N34" t="n">
-        <v>200.0</v>
+        <v>238.8</v>
       </c>
       <c r="O34" t="n">
         <v>1.0</v>
@@ -2873,7 +2873,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>510492000001231194</t>
+          <t>510492000001279066</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2893,12 +2893,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2907,21 +2907,21 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>241922</t>
+          <t>241951</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>510492000000327139</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>BATHROOMS LONDON LIMITED</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2930,10 +2930,10 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>360.0</v>
+        <v>238.8</v>
       </c>
       <c r="N35" t="n">
-        <v>360.0</v>
+        <v>238.8</v>
       </c>
       <c r="O35" t="n">
         <v>1.0</v>
@@ -2942,7 +2942,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>510492000001231242</t>
+          <t>510492000001279242</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>241925</t>
+          <t>241962</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3011,7 +3011,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>510492000001231370</t>
+          <t>510492000001279370</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3031,12 +3031,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3049,17 +3049,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>241933</t>
+          <t>241970</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>510492000001079001</t>
+          <t>510492000001144276</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>RBD Driving School</t>
+          <t>Creativa Ltd</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>200.0</v>
+        <v>240.0</v>
       </c>
       <c r="N37" t="n">
-        <v>200.0</v>
+        <v>240.0</v>
       </c>
       <c r="O37" t="n">
         <v>1.0</v>
@@ -3080,7 +3080,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>510492000001231386</t>
+          <t>510492000001288131</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3118,17 +3118,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>241934</t>
+          <t>241975</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>510492000001144276</t>
+          <t>510492000001111001</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Creativa Ltd</t>
+          <t>ABA CLEANING SERVICES LTD</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="N38" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="O38" t="n">
         <v>1.0</v>
@@ -3149,7 +3149,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>510492000001279033</t>
+          <t>510492000001300001</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3183,21 +3183,21 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>241949</t>
+          <t>241977</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000387119</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>AUTO MARKET PLACE LIMITED</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>216.4</v>
+        <v>400.0</v>
       </c>
       <c r="N39" t="n">
-        <v>238.8</v>
+        <v>400.0</v>
       </c>
       <c r="O39" t="n">
         <v>1.0</v>
@@ -3218,7 +3218,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>510492000001279066</t>
+          <t>510492000001316001</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3252,21 +3252,21 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>241951</t>
+          <t>241979</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000001064041</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>Jans Solutions Ltd</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>238.8</v>
+        <v>450.0</v>
       </c>
       <c r="N40" t="n">
-        <v>238.8</v>
+        <v>450.0</v>
       </c>
       <c r="O40" t="n">
         <v>1.0</v>
@@ -3287,7 +3287,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>510492000001279242</t>
+          <t>510492000001338001</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3325,17 +3325,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>241962</t>
+          <t>241984</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="N41" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="O41" t="n">
         <v>1.0</v>
@@ -3356,7 +3356,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>510492000001279370</t>
+          <t>510492000001338033</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3394,17 +3394,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>241970</t>
+          <t>241986</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>510492000001144276</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Creativa Ltd</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="N42" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="O42" t="n">
         <v>1.0</v>
@@ -3425,7 +3425,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>510492000001288131</t>
+          <t>510492000001338049</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3463,17 +3463,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>241975</t>
+          <t>241987</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>510492000001111001</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>ABA CLEANING SERVICES LTD</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>360.0</v>
+        <v>238.8</v>
       </c>
       <c r="N43" t="n">
-        <v>360.0</v>
+        <v>477.6</v>
       </c>
       <c r="O43" t="n">
         <v>1.0</v>
@@ -3494,7 +3494,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>510492000001300001</t>
+          <t>510492000001338066</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3532,17 +3532,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>241977</t>
+          <t>241988</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>510492000000387119</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>AUTO MARKET PLACE LIMITED</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>400.0</v>
+        <v>238.8</v>
       </c>
       <c r="N44" t="n">
-        <v>400.0</v>
+        <v>238.8</v>
       </c>
       <c r="O44" t="n">
         <v>1.0</v>
@@ -3563,7 +3563,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>510492000001316001</t>
+          <t>510492000001338242</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3583,12 +3583,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>241979</t>
+          <t>241999</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>510492000001064041</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Jans Solutions Ltd</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>450.0</v>
+        <v>240.0</v>
       </c>
       <c r="N45" t="n">
-        <v>450.0</v>
+        <v>240.0</v>
       </c>
       <c r="O45" t="n">
         <v>1.0</v>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>510492000001338001</t>
+          <t>510492000001338338</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3670,17 +3670,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>241984</t>
+          <t>242005</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N46" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O46" t="n">
         <v>1.0</v>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>510492000001338033</t>
+          <t>510492000001338370</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3739,17 +3739,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>241986</t>
+          <t>242007</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000001144276</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>Creativa Ltd</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N47" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O47" t="n">
         <v>1.0</v>
@@ -3770,7 +3770,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>510492000001338049</t>
+          <t>510492000001388001</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3790,12 +3790,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3808,17 +3808,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>241987</t>
+          <t>242021</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001088061</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>Drive with Greta</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>238.8</v>
+        <v>360.0</v>
       </c>
       <c r="N48" t="n">
-        <v>477.6</v>
+        <v>360.0</v>
       </c>
       <c r="O48" t="n">
         <v>1.0</v>
@@ -3839,7 +3839,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>510492000001338066</t>
+          <t>510492000001391088</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3877,17 +3877,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>241988</t>
+          <t>242026</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000001391079</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>NGS Plumbing &amp; Heating Ltd</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>238.8</v>
+        <v>75.0</v>
       </c>
       <c r="N49" t="n">
-        <v>238.8</v>
+        <v>75.0</v>
       </c>
       <c r="O49" t="n">
         <v>1.0</v>
@@ -3908,7 +3908,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>510492000001338242</t>
+          <t>510492000001403010</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3946,17 +3946,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>241999</t>
+          <t>242027</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000001403001</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Malvern Renovation</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>240.0</v>
+        <v>120.0</v>
       </c>
       <c r="N50" t="n">
-        <v>240.0</v>
+        <v>120.0</v>
       </c>
       <c r="O50" t="n">
         <v>1.0</v>
@@ -3977,7 +3977,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>510492000001338338</t>
+          <t>510492000001417001</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4015,17 +4015,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>242005</t>
+          <t>242032</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="N51" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="O51" t="n">
         <v>1.0</v>
@@ -4046,7 +4046,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>510492000001338370</t>
+          <t>510492000001417033</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4084,17 +4084,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>242007</t>
+          <t>242034</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>510492000001144276</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Creativa Ltd</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="N52" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="O52" t="n">
         <v>1.0</v>
@@ -4115,7 +4115,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>510492000001367083</t>
+          <t>510492000001417049</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4153,17 +4153,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>242015</t>
+          <t>242035</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>510492000000946037</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Ace Learning Plus Limited</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>450.0</v>
+        <v>477.6</v>
       </c>
       <c r="N53" t="n">
-        <v>450.0</v>
+        <v>477.6</v>
       </c>
       <c r="O53" t="n">
         <v>1.0</v>
@@ -4184,7 +4184,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>510492000001388001</t>
+          <t>510492000001417066</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4222,17 +4222,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>242021</t>
+          <t>242036</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>510492000001088061</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Drive with Greta</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>360.0</v>
+        <v>238.8</v>
       </c>
       <c r="N54" t="n">
-        <v>360.0</v>
+        <v>238.8</v>
       </c>
       <c r="O54" t="n">
         <v>1.0</v>
@@ -4253,7 +4253,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>510492000001391088</t>
+          <t>510492000001417242</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>242026</t>
+          <t>242047</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>510492000001391079</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>NGS Plumbing &amp; Heating Ltd</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>75.0</v>
+        <v>240.0</v>
       </c>
       <c r="N55" t="n">
-        <v>75.0</v>
+        <v>240.0</v>
       </c>
       <c r="O55" t="n">
         <v>1.0</v>
@@ -4322,7 +4322,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>510492000001403010</t>
+          <t>510492000001417338</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4360,17 +4360,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>242027</t>
+          <t>242053</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>510492000001403001</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Malvern Renovation</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="N56" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="O56" t="n">
         <v>1.0</v>
@@ -4391,7 +4391,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>510492000001417001</t>
+          <t>510492000001429121</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4429,17 +4429,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>242032</t>
+          <t>242060</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000970001</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>Superhouse Education Foundation</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4448,10 +4448,10 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>238.8</v>
+        <v>1000.0</v>
       </c>
       <c r="N57" t="n">
-        <v>238.8</v>
+        <v>1000.0</v>
       </c>
       <c r="O57" t="n">
         <v>1.0</v>
@@ -4460,7 +4460,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>510492000001417033</t>
+          <t>510492000001445029</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4498,17 +4498,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>242034</t>
+          <t>242065</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000001445020</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>BORN FOR IT LTD</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>238.8</v>
+        <v>660.0</v>
       </c>
       <c r="N58" t="n">
-        <v>238.8</v>
+        <v>660.0</v>
       </c>
       <c r="O58" t="n">
         <v>1.0</v>
@@ -4529,7 +4529,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>510492000001417049</t>
+          <t>510492000001450025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4563,21 +4563,21 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>242035</t>
+          <t>242068</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>477.6</v>
+        <v>718.8</v>
       </c>
       <c r="N59" t="n">
-        <v>477.6</v>
+        <v>718.8</v>
       </c>
       <c r="O59" t="n">
         <v>1.0</v>
@@ -4598,7 +4598,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>510492000001417066</t>
+          <t>510492000001359025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>242036</t>
+          <t>242012</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000317525</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>EAGLE PROPERTY CARE</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N60" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O60" t="n">
         <v>1.0</v>
@@ -4667,7 +4667,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>510492000001417162</t>
+          <t>510492000001460089</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4701,21 +4701,21 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>242042</t>
+          <t>242075</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>510492000000505059</t>
+          <t>510492000000639001</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Chorus Music Therapy &amp; Education</t>
+          <t>De'Osa Engineering Services</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4736,7 +4736,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>510492000001417242</t>
+          <t>510492000001460115</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4774,17 +4774,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>242047</t>
+          <t>242076</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000001460106</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>MOUNTAINS OF GLORY</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>240.0</v>
+        <v>250.0</v>
       </c>
       <c r="N62" t="n">
-        <v>240.0</v>
+        <v>250.0</v>
       </c>
       <c r="O62" t="n">
         <v>1.0</v>
@@ -4805,7 +4805,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>510492000001417338</t>
+          <t>510492000001460138</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4843,17 +4843,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>242053</t>
+          <t>242077</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000386033</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>ALPHA EUROPE LTD</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4874,7 +4874,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>510492000001429121</t>
+          <t>510492000001482001</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4912,17 +4912,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>242060</t>
+          <t>242082</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>510492000000970001</t>
+          <t>510492000001057001</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Superhouse Education Foundation</t>
+          <t>Corby Motors Ltd</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>1000.0</v>
+        <v>55.0</v>
       </c>
       <c r="N64" t="n">
-        <v>1000.0</v>
+        <v>555.0</v>
       </c>
       <c r="O64" t="n">
         <v>1.0</v>
@@ -4943,7 +4943,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>510492000001445029</t>
+          <t>510492000001482018</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>242065</t>
+          <t>242083</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>510492000001445020</t>
+          <t>510492000001413024</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>BORN FOR IT LTD</t>
+          <t>88 DRIVING SCHOOL LTD</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>660.0</v>
+        <v>110.0</v>
       </c>
       <c r="N65" t="n">
-        <v>660.0</v>
+        <v>110.0</v>
       </c>
       <c r="O65" t="n">
         <v>1.0</v>
@@ -5012,7 +5012,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>510492000001450008</t>
+          <t>510492000001367115</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5050,17 +5050,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>242067</t>
+          <t>242017</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>510492000000327139</t>
+          <t>510492000001025001</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>BATHROOMS LONDON LIMITED</t>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>400.0</v>
+        <v>310.3</v>
       </c>
       <c r="N66" t="n">
-        <v>400.0</v>
+        <v>310.3</v>
       </c>
       <c r="O66" t="n">
         <v>1.0</v>
@@ -5081,7 +5081,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>510492000001450025</t>
+          <t>510492000001486010</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5115,11 +5115,11 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>242068</t>
+          <t>242085</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>718.8</v>
+        <v>238.8</v>
       </c>
       <c r="N67" t="n">
-        <v>718.8</v>
+        <v>238.8</v>
       </c>
       <c r="O67" t="n">
         <v>1.0</v>
@@ -5150,7 +5150,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>510492000001359025</t>
+          <t>510492000001486042</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5188,17 +5188,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>242012</t>
+          <t>242087</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>510492000000317525</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>EAGLE PROPERTY CARE</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="N68" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="O68" t="n">
         <v>1.0</v>
@@ -5219,7 +5219,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>510492000001460089</t>
+          <t>510492000001486058</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5257,17 +5257,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>242075</t>
+          <t>242088</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>510492000000639001</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>De'Osa Engineering Services</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>120.0</v>
+        <v>477.6</v>
       </c>
       <c r="N69" t="n">
-        <v>120.0</v>
+        <v>477.6</v>
       </c>
       <c r="O69" t="n">
         <v>1.0</v>
@@ -5288,7 +5288,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>510492000001460115</t>
+          <t>510492000001486075</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>242076</t>
+          <t>242089</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>510492000001460106</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>MOUNTAINS OF GLORY</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>250.0</v>
+        <v>238.8</v>
       </c>
       <c r="N70" t="n">
-        <v>250.0</v>
+        <v>238.8</v>
       </c>
       <c r="O70" t="n">
         <v>1.0</v>
@@ -5357,7 +5357,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>510492000001460138</t>
+          <t>510492000001486171</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5395,17 +5395,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>242077</t>
+          <t>242095</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>510492000000386033</t>
+          <t>510492000000505059</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>ALPHA EUROPE LTD</t>
+          <t>Chorus Music Therapy &amp; Education</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>240.0</v>
+        <v>120.0</v>
       </c>
       <c r="N71" t="n">
-        <v>240.0</v>
+        <v>120.0</v>
       </c>
       <c r="O71" t="n">
         <v>1.0</v>
@@ -5426,7 +5426,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>510492000001474010</t>
+          <t>510492000001486347</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5464,17 +5464,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>242080</t>
+          <t>242106</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>510492000001474001</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>First Class Learning Reading Central</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>270.0</v>
+        <v>240.0</v>
       </c>
       <c r="N72" t="n">
-        <v>270.0</v>
+        <v>240.0</v>
       </c>
       <c r="O72" t="n">
         <v>1.0</v>
@@ -5495,7 +5495,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>510492000001477103</t>
+          <t>510492000001496109</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5533,17 +5533,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>242081</t>
+          <t>242114</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>510492000000541229</t>
+          <t>510492000001378001</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Optimum Global Care</t>
+          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5552,983 +5552,17 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>120.0</v>
+        <v>270.0</v>
       </c>
       <c r="N73" t="n">
-        <v>120.0</v>
+        <v>270.0</v>
       </c>
       <c r="O73" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>510492000001482001</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>242082</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>510492000001057001</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Corby Motors Ltd</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M74" t="n">
-        <v>555.0</v>
-      </c>
-      <c r="N74" t="n">
-        <v>555.0</v>
-      </c>
-      <c r="O74" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>510492000001482018</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H75" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>242083</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>510492000001413024</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>88 DRIVING SCHOOL LTD</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M75" t="n">
-        <v>110.0</v>
-      </c>
-      <c r="N75" t="n">
-        <v>110.0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>510492000001488015</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H76" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>242084</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>510492000001488006</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>SPOT CLEANERS LTD</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M76" t="n">
-        <v>130.0</v>
-      </c>
-      <c r="N76" t="n">
-        <v>130.0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>510492000001367115</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H77" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>242017</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>510492000001025001</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M77" t="n">
-        <v>310.3</v>
-      </c>
-      <c r="N77" t="n">
-        <v>310.3</v>
-      </c>
-      <c r="O77" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>510492000001486010</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H78" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>242085</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>510492000000122647</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M78" t="n">
-        <v>238.8</v>
-      </c>
-      <c r="N78" t="n">
-        <v>238.8</v>
-      </c>
-      <c r="O78" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>510492000001486042</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H79" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>242087</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>510492000000123247</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>NOMADS CLOTHING LIMITED</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M79" t="n">
-        <v>238.8</v>
-      </c>
-      <c r="N79" t="n">
-        <v>238.8</v>
-      </c>
-      <c r="O79" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>510492000001486058</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H80" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>242088</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>510492000000123277</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Patrick Shoes Limited</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M80" t="n">
-        <v>477.6</v>
-      </c>
-      <c r="N80" t="n">
-        <v>477.6</v>
-      </c>
-      <c r="O80" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>510492000001486075</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H81" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>242089</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>510492000000192073</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M81" t="n">
-        <v>238.8</v>
-      </c>
-      <c r="N81" t="n">
-        <v>238.8</v>
-      </c>
-      <c r="O81" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>510492000001486171</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H82" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>242095</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>510492000000505059</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Chorus Music Therapy &amp; Education</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M82" t="n">
-        <v>120.0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>120.0</v>
-      </c>
-      <c r="O82" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>510492000001486235</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H83" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>242099</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>510492000000742001</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Adam’s Painting and Decorating</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M83" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="N83" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="O83" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>510492000001486347</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H84" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>242106</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>510492000000123277</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Patrick Shoes Limited</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M84" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="N84" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="O84" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>510492000001496082</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H85" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>242113</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>510492000001155001</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Galloway Pest Control</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M85" t="n">
-        <v>360.0</v>
-      </c>
-      <c r="N85" t="n">
-        <v>360.0</v>
-      </c>
-      <c r="O85" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>510492000001496003</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H86" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>242112</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>510492000000822033</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Sofiya Designs Limited</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M86" t="n">
-        <v>420.0</v>
-      </c>
-      <c r="N86" t="n">
-        <v>420.0</v>
-      </c>
-      <c r="O86" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>510492000001496109</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H87" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>242114</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>510492000001378001</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M87" t="n">
-        <v>270.0</v>
-      </c>
-      <c r="N87" t="n">
-        <v>270.0</v>
-      </c>
-      <c r="O87" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="55" t="inlineStr">
+      <c r="A74" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6537,7 +5571,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A88:O88"/>
+    <mergeCell ref="A74:O74"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_overdue_zoho.xlsx
+++ b/AR_overdue_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:O76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 09/09/2026</t>
+As of 16/09/2026</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>340</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>284</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>284</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>253</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>253</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>253</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>222</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>222</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>219</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>219</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4598,7 +4598,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>510492000001359025</t>
+          <t>510492000001460089</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>242012</t>
+          <t>242075</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>510492000000317525</t>
+          <t>510492000000639001</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>EAGLE PROPERTY CARE</t>
+          <t>De'Osa Engineering Services</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>240.0</v>
+        <v>120.0</v>
       </c>
       <c r="N60" t="n">
-        <v>240.0</v>
+        <v>120.0</v>
       </c>
       <c r="O60" t="n">
         <v>1.0</v>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>510492000001460089</t>
+          <t>510492000001460115</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4705,17 +4705,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>242075</t>
+          <t>242076</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>510492000000639001</t>
+          <t>510492000001460106</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>De'Osa Engineering Services</t>
+          <t>MOUNTAINS OF GLORY</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>120.0</v>
+        <v>250.0</v>
       </c>
       <c r="N61" t="n">
-        <v>120.0</v>
+        <v>250.0</v>
       </c>
       <c r="O61" t="n">
         <v>1.0</v>
@@ -4736,7 +4736,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>510492000001460115</t>
+          <t>510492000001460138</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4774,17 +4774,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>242076</t>
+          <t>242077</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>510492000001460106</t>
+          <t>510492000000386033</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>MOUNTAINS OF GLORY</t>
+          <t>ALPHA EUROPE LTD</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>250.0</v>
+        <v>240.0</v>
       </c>
       <c r="N62" t="n">
-        <v>250.0</v>
+        <v>240.0</v>
       </c>
       <c r="O62" t="n">
         <v>1.0</v>
@@ -4805,7 +4805,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>510492000001460138</t>
+          <t>510492000001359025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4843,17 +4843,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>242077</t>
+          <t>242012</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>510492000000386033</t>
+          <t>510492000000317525</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>ALPHA EUROPE LTD</t>
+          <t>EAGLE PROPERTY CARE</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5562,7 +5562,145 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="55" t="inlineStr">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>510492000001506012</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>242115</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>510492000001506003</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Mrs. Almina Dhalla</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>510492000001510042</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>242118</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>510492000001488006</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>SPOT CLEANERS LTD</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>130.0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>130.0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5571,7 +5709,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A74:O74"/>
+    <mergeCell ref="A76:O76"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_overdue_zoho.xlsx
+++ b/AR_overdue_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O76"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 16/09/2026</t>
+As of 18/09/2026</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>342</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>302</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>286</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>286</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>224</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>224</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>221</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>221</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>208</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>86</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4391,7 +4391,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>510492000001429121</t>
+          <t>510492000001445029</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4429,17 +4429,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>242060</t>
+          <t>242065</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>510492000000970001</t>
+          <t>510492000001445020</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Superhouse Education Foundation</t>
+          <t>BORN FOR IT LTD</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4448,10 +4448,10 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>1000.0</v>
+        <v>660.0</v>
       </c>
       <c r="N57" t="n">
-        <v>1000.0</v>
+        <v>660.0</v>
       </c>
       <c r="O57" t="n">
         <v>1.0</v>
@@ -4460,7 +4460,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>510492000001445029</t>
+          <t>510492000001450025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4494,21 +4494,21 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>242065</t>
+          <t>242068</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>510492000001445020</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>BORN FOR IT LTD</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>660.0</v>
+        <v>718.8</v>
       </c>
       <c r="N58" t="n">
-        <v>660.0</v>
+        <v>718.8</v>
       </c>
       <c r="O58" t="n">
         <v>1.0</v>
@@ -4529,7 +4529,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>510492000001450025</t>
+          <t>510492000001460089</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4563,21 +4563,21 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>242068</t>
+          <t>242075</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000639001</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>De'Osa Engineering Services</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>718.8</v>
+        <v>120.0</v>
       </c>
       <c r="N59" t="n">
-        <v>718.8</v>
+        <v>120.0</v>
       </c>
       <c r="O59" t="n">
         <v>1.0</v>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>510492000001460089</t>
+          <t>510492000001460115</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>242075</t>
+          <t>242076</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>510492000000639001</t>
+          <t>510492000001460106</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>De'Osa Engineering Services</t>
+          <t>MOUNTAINS OF GLORY</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>120.0</v>
+        <v>250.0</v>
       </c>
       <c r="N60" t="n">
-        <v>120.0</v>
+        <v>250.0</v>
       </c>
       <c r="O60" t="n">
         <v>1.0</v>
@@ -4667,7 +4667,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>510492000001460115</t>
+          <t>510492000001460138</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4705,17 +4705,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>242076</t>
+          <t>242077</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>510492000001460106</t>
+          <t>510492000000386033</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>MOUNTAINS OF GLORY</t>
+          <t>ALPHA EUROPE LTD</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>250.0</v>
+        <v>240.0</v>
       </c>
       <c r="N61" t="n">
-        <v>250.0</v>
+        <v>240.0</v>
       </c>
       <c r="O61" t="n">
         <v>1.0</v>
@@ -4736,7 +4736,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>510492000001460138</t>
+          <t>510492000001359025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4774,17 +4774,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>242077</t>
+          <t>242012</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>510492000000386033</t>
+          <t>510492000000317525</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>ALPHA EUROPE LTD</t>
+          <t>EAGLE PROPERTY CARE</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4805,7 +4805,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>510492000001359025</t>
+          <t>510492000001482001</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4843,17 +4843,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>242012</t>
+          <t>242082</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>510492000000317525</t>
+          <t>510492000001057001</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>EAGLE PROPERTY CARE</t>
+          <t>Corby Motors Ltd</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>240.0</v>
+        <v>55.0</v>
       </c>
       <c r="N63" t="n">
-        <v>240.0</v>
+        <v>555.0</v>
       </c>
       <c r="O63" t="n">
         <v>1.0</v>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>510492000001482001</t>
+          <t>510492000001482018</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4912,17 +4912,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>242082</t>
+          <t>242083</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>510492000001057001</t>
+          <t>510492000001413024</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Corby Motors Ltd</t>
+          <t>88 DRIVING SCHOOL LTD</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>55.0</v>
+        <v>110.0</v>
       </c>
       <c r="N64" t="n">
-        <v>555.0</v>
+        <v>110.0</v>
       </c>
       <c r="O64" t="n">
         <v>1.0</v>
@@ -4943,7 +4943,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>510492000001482018</t>
+          <t>510492000001367115</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>242083</t>
+          <t>242017</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>510492000001413024</t>
+          <t>510492000001025001</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>88 DRIVING SCHOOL LTD</t>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>110.0</v>
+        <v>310.3</v>
       </c>
       <c r="N65" t="n">
-        <v>110.0</v>
+        <v>310.3</v>
       </c>
       <c r="O65" t="n">
         <v>1.0</v>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>510492000001367115</t>
+          <t>510492000001486010</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5050,17 +5050,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>242017</t>
+          <t>242085</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>510492000001025001</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>310.3</v>
+        <v>238.8</v>
       </c>
       <c r="N66" t="n">
-        <v>310.3</v>
+        <v>238.8</v>
       </c>
       <c r="O66" t="n">
         <v>1.0</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>510492000001486010</t>
+          <t>510492000001486042</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5119,17 +5119,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>242085</t>
+          <t>242087</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>510492000001486042</t>
+          <t>510492000001486058</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5188,17 +5188,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>242087</t>
+          <t>242088</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="N68" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O68" t="n">
         <v>1.0</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>510492000001486058</t>
+          <t>510492000001486075</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5257,17 +5257,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>242088</t>
+          <t>242089</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="N69" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="O69" t="n">
         <v>1.0</v>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>510492000001486075</t>
+          <t>510492000001486171</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>242089</t>
+          <t>242095</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000505059</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>Chorus Music Therapy &amp; Education</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="N70" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="O70" t="n">
         <v>1.0</v>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>510492000001486171</t>
+          <t>510492000001486347</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5395,17 +5395,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>242095</t>
+          <t>242106</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>510492000000505059</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Chorus Music Therapy &amp; Education</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="N71" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="O71" t="n">
         <v>1.0</v>
@@ -5426,7 +5426,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>510492000001486347</t>
+          <t>510492000001496109</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5464,17 +5464,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>242106</t>
+          <t>242114</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001378001</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>240.0</v>
+        <v>270.0</v>
       </c>
       <c r="N72" t="n">
-        <v>240.0</v>
+        <v>270.0</v>
       </c>
       <c r="O72" t="n">
         <v>1.0</v>
@@ -5495,7 +5495,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>510492000001496109</t>
+          <t>510492000001506012</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5533,17 +5533,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>242114</t>
+          <t>242115</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>510492000001378001</t>
+          <t>510492000001506003</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
+          <t>Mrs. Almina Dhalla</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>270.0</v>
+        <v>300.0</v>
       </c>
       <c r="N73" t="n">
-        <v>270.0</v>
+        <v>300.0</v>
       </c>
       <c r="O73" t="n">
         <v>1.0</v>
@@ -5564,7 +5564,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>510492000001506012</t>
+          <t>510492000001510042</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5602,17 +5602,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>242115</t>
+          <t>242118</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>510492000001506003</t>
+          <t>510492000001488006</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Mrs. Almina Dhalla</t>
+          <t>SPOT CLEANERS LTD</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5621,10 +5621,10 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>300.0</v>
+        <v>130.0</v>
       </c>
       <c r="N74" t="n">
-        <v>300.0</v>
+        <v>130.0</v>
       </c>
       <c r="O74" t="n">
         <v>1.0</v>
@@ -5633,7 +5633,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>510492000001510042</t>
+          <t>510492000001514001</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5653,54 +5653,123 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>242119</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>510492000001378001</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>540.0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>540.0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>510492000001517010</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H75" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>242118</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>510492000001488006</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>SPOT CLEANERS LTD</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M75" t="n">
-        <v>130.0</v>
-      </c>
-      <c r="N75" t="n">
-        <v>130.0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="55" t="inlineStr">
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>242120</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>510492000001517001</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Max Out Tutoring</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>480.0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>480.0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5709,7 +5778,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A76:O76"/>
+    <mergeCell ref="A77:O77"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_overdue_zoho.xlsx
+++ b/AR_overdue_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O73"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>510492000001338001</t>
+          <t>510492000001338033</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3325,17 +3325,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>241984</t>
+          <t>241986</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>510492000001338033</t>
+          <t>510492000001338049</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3394,17 +3394,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>241986</t>
+          <t>241987</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3416,7 +3416,7 @@
         <v>238.8</v>
       </c>
       <c r="N42" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O42" t="n">
         <v>1.0</v>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>510492000001338049</t>
+          <t>510492000001338066</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3463,17 +3463,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>241987</t>
+          <t>241988</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3485,7 +3485,7 @@
         <v>238.8</v>
       </c>
       <c r="N43" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="O43" t="n">
         <v>1.0</v>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>510492000001338066</t>
+          <t>510492000001338242</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3532,17 +3532,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>241988</t>
+          <t>241999</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N44" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O44" t="n">
         <v>1.0</v>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>510492000001338242</t>
+          <t>510492000001338338</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>241999</t>
+          <t>242005</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>510492000001338338</t>
+          <t>510492000001338370</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3670,17 +3670,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>242005</t>
+          <t>242007</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001144276</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>Creativa Ltd</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3701,7 +3701,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>510492000001338370</t>
+          <t>510492000001388001</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3739,17 +3739,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>242007</t>
+          <t>242021</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>510492000001144276</t>
+          <t>510492000001088061</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Creativa Ltd</t>
+          <t>Drive with Greta</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="N47" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="O47" t="n">
         <v>1.0</v>
@@ -3770,7 +3770,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>510492000001388001</t>
+          <t>510492000001391088</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3790,12 +3790,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3808,17 +3808,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>242021</t>
+          <t>242026</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>510492000001088061</t>
+          <t>510492000001391079</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Drive with Greta</t>
+          <t>NGS Plumbing &amp; Heating Ltd</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>360.0</v>
+        <v>75.0</v>
       </c>
       <c r="N48" t="n">
-        <v>360.0</v>
+        <v>75.0</v>
       </c>
       <c r="O48" t="n">
         <v>1.0</v>
@@ -3839,7 +3839,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>510492000001391088</t>
+          <t>510492000001403010</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3877,17 +3877,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>242026</t>
+          <t>242027</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>510492000001391079</t>
+          <t>510492000001403001</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>NGS Plumbing &amp; Heating Ltd</t>
+          <t>Malvern Renovation</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>75.0</v>
+        <v>120.0</v>
       </c>
       <c r="N49" t="n">
-        <v>75.0</v>
+        <v>120.0</v>
       </c>
       <c r="O49" t="n">
         <v>1.0</v>
@@ -3908,7 +3908,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>510492000001403010</t>
+          <t>510492000001417001</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3946,17 +3946,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>242027</t>
+          <t>242032</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>510492000001403001</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Malvern Renovation</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>120.0</v>
+        <v>238.8</v>
       </c>
       <c r="N50" t="n">
-        <v>120.0</v>
+        <v>238.8</v>
       </c>
       <c r="O50" t="n">
         <v>1.0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>510492000001417001</t>
+          <t>510492000001417033</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4015,17 +4015,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>242032</t>
+          <t>242034</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>510492000001417033</t>
+          <t>510492000001417049</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4084,17 +4084,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>242034</t>
+          <t>242035</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="N52" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O52" t="n">
         <v>1.0</v>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>510492000001417049</t>
+          <t>510492000001417066</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4153,17 +4153,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>242035</t>
+          <t>242036</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="N53" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="O53" t="n">
         <v>1.0</v>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>510492000001417066</t>
+          <t>510492000001417242</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4222,17 +4222,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>242036</t>
+          <t>242047</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N54" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O54" t="n">
         <v>1.0</v>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>510492000001417242</t>
+          <t>510492000001417338</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>242047</t>
+          <t>242053</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4322,7 +4322,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>510492000001417338</t>
+          <t>510492000001445029</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4360,17 +4360,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>242053</t>
+          <t>242065</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001445020</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>BORN FOR IT LTD</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>240.0</v>
+        <v>660.0</v>
       </c>
       <c r="N56" t="n">
-        <v>240.0</v>
+        <v>660.0</v>
       </c>
       <c r="O56" t="n">
         <v>1.0</v>
@@ -4391,7 +4391,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>510492000001445029</t>
+          <t>510492000001450025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4425,21 +4425,21 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>242065</t>
+          <t>242068</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>510492000001445020</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>BORN FOR IT LTD</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4448,10 +4448,10 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>660.0</v>
+        <v>718.8</v>
       </c>
       <c r="N57" t="n">
-        <v>660.0</v>
+        <v>718.8</v>
       </c>
       <c r="O57" t="n">
         <v>1.0</v>
@@ -4460,7 +4460,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>510492000001450025</t>
+          <t>510492000001460089</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4494,21 +4494,21 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>242068</t>
+          <t>242075</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000639001</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>De'Osa Engineering Services</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>718.8</v>
+        <v>120.0</v>
       </c>
       <c r="N58" t="n">
-        <v>718.8</v>
+        <v>120.0</v>
       </c>
       <c r="O58" t="n">
         <v>1.0</v>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>510492000001460089</t>
+          <t>510492000001460115</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4567,17 +4567,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>242075</t>
+          <t>242076</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>510492000000639001</t>
+          <t>510492000001460106</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>De'Osa Engineering Services</t>
+          <t>MOUNTAINS OF GLORY</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>120.0</v>
+        <v>250.0</v>
       </c>
       <c r="N59" t="n">
-        <v>120.0</v>
+        <v>250.0</v>
       </c>
       <c r="O59" t="n">
         <v>1.0</v>
@@ -4598,7 +4598,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>510492000001460115</t>
+          <t>510492000001460138</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>242076</t>
+          <t>242077</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>510492000001460106</t>
+          <t>510492000000386033</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>MOUNTAINS OF GLORY</t>
+          <t>ALPHA EUROPE LTD</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>250.0</v>
+        <v>240.0</v>
       </c>
       <c r="N60" t="n">
-        <v>250.0</v>
+        <v>240.0</v>
       </c>
       <c r="O60" t="n">
         <v>1.0</v>
@@ -4667,7 +4667,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>510492000001460138</t>
+          <t>510492000001359025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4705,17 +4705,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>242077</t>
+          <t>242012</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>510492000000386033</t>
+          <t>510492000000317525</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>ALPHA EUROPE LTD</t>
+          <t>EAGLE PROPERTY CARE</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4736,7 +4736,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>510492000001359025</t>
+          <t>510492000001482001</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4774,17 +4774,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>242012</t>
+          <t>242082</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>510492000000317525</t>
+          <t>510492000001057001</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>EAGLE PROPERTY CARE</t>
+          <t>Corby Motors Ltd</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>240.0</v>
+        <v>55.0</v>
       </c>
       <c r="N62" t="n">
-        <v>240.0</v>
+        <v>555.0</v>
       </c>
       <c r="O62" t="n">
         <v>1.0</v>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>510492000001482001</t>
+          <t>510492000001482018</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4843,17 +4843,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>242082</t>
+          <t>242083</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>510492000001057001</t>
+          <t>510492000001413024</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Corby Motors Ltd</t>
+          <t>88 DRIVING SCHOOL LTD</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>55.0</v>
+        <v>110.0</v>
       </c>
       <c r="N63" t="n">
-        <v>555.0</v>
+        <v>110.0</v>
       </c>
       <c r="O63" t="n">
         <v>1.0</v>
@@ -4874,7 +4874,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>510492000001482018</t>
+          <t>510492000001486010</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4912,17 +4912,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>242083</t>
+          <t>242085</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>510492000001413024</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>88 DRIVING SCHOOL LTD</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>110.0</v>
+        <v>238.8</v>
       </c>
       <c r="N64" t="n">
-        <v>110.0</v>
+        <v>238.8</v>
       </c>
       <c r="O64" t="n">
         <v>1.0</v>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>510492000001367115</t>
+          <t>510492000001486042</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>242017</t>
+          <t>242087</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>510492000001025001</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>310.3</v>
+        <v>238.8</v>
       </c>
       <c r="N65" t="n">
-        <v>310.3</v>
+        <v>238.8</v>
       </c>
       <c r="O65" t="n">
         <v>1.0</v>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>510492000001486010</t>
+          <t>510492000001486058</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5050,17 +5050,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>242085</t>
+          <t>242088</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="N66" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O66" t="n">
         <v>1.0</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>510492000001486042</t>
+          <t>510492000001486075</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5119,17 +5119,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>242087</t>
+          <t>242089</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>510492000001486058</t>
+          <t>510492000001486171</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5188,17 +5188,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>242088</t>
+          <t>242095</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000505059</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>Chorus Music Therapy &amp; Education</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>477.6</v>
+        <v>120.0</v>
       </c>
       <c r="N68" t="n">
-        <v>477.6</v>
+        <v>120.0</v>
       </c>
       <c r="O68" t="n">
         <v>1.0</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>510492000001486075</t>
+          <t>510492000001486347</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5257,17 +5257,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>242089</t>
+          <t>242106</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N69" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O69" t="n">
         <v>1.0</v>
@@ -5288,7 +5288,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>510492000001486171</t>
+          <t>510492000001496109</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>242095</t>
+          <t>242114</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>510492000000505059</t>
+          <t>510492000001378001</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Chorus Music Therapy &amp; Education</t>
+          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>120.0</v>
+        <v>270.0</v>
       </c>
       <c r="N70" t="n">
-        <v>120.0</v>
+        <v>270.0</v>
       </c>
       <c r="O70" t="n">
         <v>1.0</v>
@@ -5357,7 +5357,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>510492000001486347</t>
+          <t>510492000001510042</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5395,17 +5395,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>242106</t>
+          <t>242118</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001488006</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>SPOT CLEANERS LTD</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>240.0</v>
+        <v>130.0</v>
       </c>
       <c r="N71" t="n">
-        <v>240.0</v>
+        <v>130.0</v>
       </c>
       <c r="O71" t="n">
         <v>1.0</v>
@@ -5426,7 +5426,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>510492000001496109</t>
+          <t>510492000001517010</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5464,17 +5464,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>242114</t>
+          <t>242120</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>510492000001378001</t>
+          <t>510492000001517001</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
+          <t>Max Out Tutoring</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5483,293 +5483,17 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>270.0</v>
+        <v>120.0</v>
       </c>
       <c r="N72" t="n">
-        <v>270.0</v>
+        <v>480.0</v>
       </c>
       <c r="O72" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>510492000001506012</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>242115</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>510492000001506003</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Mrs. Almina Dhalla</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M73" t="n">
-        <v>300.0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>300.0</v>
-      </c>
-      <c r="O73" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>510492000001510042</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>242118</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>510492000001488006</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>SPOT CLEANERS LTD</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M74" t="n">
-        <v>130.0</v>
-      </c>
-      <c r="N74" t="n">
-        <v>130.0</v>
-      </c>
-      <c r="O74" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>510492000001514001</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H75" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>242119</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>510492000001378001</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M75" t="n">
-        <v>540.0</v>
-      </c>
-      <c r="N75" t="n">
-        <v>540.0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>510492000001517010</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H76" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>242120</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>510492000001517001</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Max Out Tutoring</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M76" t="n">
-        <v>480.0</v>
-      </c>
-      <c r="N76" t="n">
-        <v>480.0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="55" t="inlineStr">
+      <c r="A73" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5778,7 +5502,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A77:O77"/>
+    <mergeCell ref="A73:O73"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_overdue_zoho.xlsx
+++ b/AR_overdue_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O73"/>
+  <dimension ref="A1:O78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 18/09/2026</t>
+As of 23/09/2026</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>347</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>307</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>291</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>291</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>260</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>260</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>260</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>229</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>229</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>226</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>226</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>213</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>207</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>191</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>91</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4460,7 +4460,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>510492000001460089</t>
+          <t>510492000001359025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4498,17 +4498,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>242075</t>
+          <t>242012</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>510492000000639001</t>
+          <t>510492000000317525</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>De'Osa Engineering Services</t>
+          <t>EAGLE PROPERTY CARE</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="N58" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="O58" t="n">
         <v>1.0</v>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>510492000001460115</t>
+          <t>510492000001460089</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4567,17 +4567,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>242076</t>
+          <t>242075</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>510492000001460106</t>
+          <t>510492000000639001</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>MOUNTAINS OF GLORY</t>
+          <t>De'Osa Engineering Services</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>250.0</v>
+        <v>120.0</v>
       </c>
       <c r="N59" t="n">
-        <v>250.0</v>
+        <v>120.0</v>
       </c>
       <c r="O59" t="n">
         <v>1.0</v>
@@ -4598,7 +4598,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>510492000001460138</t>
+          <t>510492000001460115</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>242077</t>
+          <t>242076</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>510492000000386033</t>
+          <t>510492000001460106</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>ALPHA EUROPE LTD</t>
+          <t>MOUNTAINS OF GLORY</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>240.0</v>
+        <v>250.0</v>
       </c>
       <c r="N60" t="n">
-        <v>240.0</v>
+        <v>250.0</v>
       </c>
       <c r="O60" t="n">
         <v>1.0</v>
@@ -4667,7 +4667,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>510492000001359025</t>
+          <t>510492000001460138</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4705,17 +4705,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>242012</t>
+          <t>242077</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>510492000000317525</t>
+          <t>510492000000386033</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>EAGLE PROPERTY CARE</t>
+          <t>ALPHA EUROPE LTD</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5493,7 +5493,352 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="55" t="inlineStr">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>510492000001517029</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>242121</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>510492000001517001</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Max Out Tutoring</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>480.0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>480.0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>510492000001517056</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>242122</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>510492000001088061</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Drive with Greta</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="N74" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>510492000001517086</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>242124</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>510492000001260001</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Elite Learning Epsom Ltd</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>57.24</v>
+      </c>
+      <c r="N75" t="n">
+        <v>57.24</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>510492000001517128</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>242127</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>510492000001025001</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>125.0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>375.0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>510492000001527001</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>242128</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>510492000000256001</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>OPTIMUM GLOBAL LINKS</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5502,7 +5847,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A73:O73"/>
+    <mergeCell ref="A78:O78"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_overdue_zoho.xlsx
+++ b/AR_overdue_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 23/09/2026</t>
+As of 25/09/2026</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>349</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>309</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>293</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>293</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>262</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>262</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>262</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>231</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>231</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>228</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>228</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>215</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>209</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>203</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>203</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1976,7 +1976,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>510492000001141001</t>
+          <t>510492000001144294</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2014,17 +2014,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>241868</t>
+          <t>241869</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>510492000001135181</t>
+          <t>510492000001144276</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Greyson Studios</t>
+          <t>Creativa Ltd</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>150.0</v>
+        <v>240.0</v>
       </c>
       <c r="N22" t="n">
-        <v>150.0</v>
+        <v>240.0</v>
       </c>
       <c r="O22" t="n">
         <v>1.0</v>
@@ -2045,7 +2045,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>510492000001144294</t>
+          <t>510492000001180143</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2079,21 +2079,21 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>241869</t>
+          <t>241878</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>510492000001144276</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Creativa Ltd</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="N23" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="O23" t="n">
         <v>1.0</v>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>510492000001180143</t>
+          <t>510492000001180178</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>241878</t>
+          <t>241879</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000240001</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>Cameraboss Photography</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>238.8</v>
+        <v>200.0</v>
       </c>
       <c r="N24" t="n">
-        <v>238.8</v>
+        <v>200.0</v>
       </c>
       <c r="O24" t="n">
         <v>1.0</v>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>510492000001180178</t>
+          <t>510492000001180423</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2221,17 +2221,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>241879</t>
+          <t>241886</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>510492000000240001</t>
+          <t>510492000000327139</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Cameraboss Photography</t>
+          <t>BATHROOMS LONDON LIMITED</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>200.0</v>
+        <v>360.0</v>
       </c>
       <c r="N25" t="n">
-        <v>200.0</v>
+        <v>360.0</v>
       </c>
       <c r="O25" t="n">
         <v>1.0</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>510492000001180423</t>
+          <t>510492000001180633</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2272,12 +2272,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2290,17 +2290,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>241886</t>
+          <t>241892</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>510492000000327139</t>
+          <t>510492000000792001</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>BATHROOMS LONDON LIMITED</t>
+          <t>Edens Edge Limited</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>360.0</v>
+        <v>240.0</v>
       </c>
       <c r="N26" t="n">
-        <v>360.0</v>
+        <v>240.0</v>
       </c>
       <c r="O26" t="n">
         <v>1.0</v>
@@ -2321,7 +2321,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>510492000001180633</t>
+          <t>510492000001231066</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>241892</t>
+          <t>241914</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>510492000000792001</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Edens Edge Limited</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="N27" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="O27" t="n">
         <v>1.0</v>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>510492000001231066</t>
+          <t>510492000001231082</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2424,21 +2424,21 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>241914</t>
+          <t>241915</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000240001</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>Cameraboss Photography</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>238.8</v>
+        <v>200.0</v>
       </c>
       <c r="N28" t="n">
-        <v>238.8</v>
+        <v>200.0</v>
       </c>
       <c r="O28" t="n">
         <v>1.0</v>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>510492000001231082</t>
+          <t>510492000001231194</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2497,17 +2497,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>241915</t>
+          <t>241922</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>510492000000240001</t>
+          <t>510492000000327139</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Cameraboss Photography</t>
+          <t>BATHROOMS LONDON LIMITED</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>200.0</v>
+        <v>360.0</v>
       </c>
       <c r="N29" t="n">
-        <v>200.0</v>
+        <v>360.0</v>
       </c>
       <c r="O29" t="n">
         <v>1.0</v>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>510492000001231194</t>
+          <t>510492000001231242</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2566,17 +2566,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>241922</t>
+          <t>241925</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>510492000000327139</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>BATHROOMS LONDON LIMITED</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>360.0</v>
+        <v>240.0</v>
       </c>
       <c r="N30" t="n">
-        <v>360.0</v>
+        <v>240.0</v>
       </c>
       <c r="O30" t="n">
         <v>1.0</v>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>510492000001231242</t>
+          <t>510492000001231370</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2635,17 +2635,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>241925</t>
+          <t>241933</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000001079001</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>RBD Driving School</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>240.0</v>
+        <v>200.0</v>
       </c>
       <c r="N31" t="n">
-        <v>240.0</v>
+        <v>200.0</v>
       </c>
       <c r="O31" t="n">
         <v>1.0</v>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>510492000001231370</t>
+          <t>510492000001231386</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2704,17 +2704,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>241933</t>
+          <t>241934</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>510492000001079001</t>
+          <t>510492000001144276</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>RBD Driving School</t>
+          <t>Creativa Ltd</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>200.0</v>
+        <v>240.0</v>
       </c>
       <c r="N32" t="n">
-        <v>200.0</v>
+        <v>240.0</v>
       </c>
       <c r="O32" t="n">
         <v>1.0</v>
@@ -2735,7 +2735,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>510492000001231386</t>
+          <t>510492000001279033</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2769,21 +2769,21 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>241934</t>
+          <t>241949</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>510492000001144276</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Creativa Ltd</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>240.0</v>
+        <v>216.4</v>
       </c>
       <c r="N33" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="O33" t="n">
         <v>1.0</v>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>510492000001279033</t>
+          <t>510492000001279066</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2842,17 +2842,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>241949</t>
+          <t>241951</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>216.4</v>
+        <v>238.8</v>
       </c>
       <c r="N34" t="n">
         <v>238.8</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>510492000001279066</t>
+          <t>510492000001279242</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2907,21 +2907,21 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>241951</t>
+          <t>241962</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2930,10 +2930,10 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N35" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O35" t="n">
         <v>1.0</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>510492000001279242</t>
+          <t>510492000001279370</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2980,17 +2980,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>241962</t>
+          <t>241970</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000001144276</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Creativa Ltd</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3011,7 +3011,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>510492000001279370</t>
+          <t>510492000001288131</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3031,12 +3031,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3049,17 +3049,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>241970</t>
+          <t>241975</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>510492000001144276</t>
+          <t>510492000001111001</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Creativa Ltd</t>
+          <t>ABA CLEANING SERVICES LTD</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="N37" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="O37" t="n">
         <v>1.0</v>
@@ -3080,7 +3080,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>510492000001288131</t>
+          <t>510492000001300001</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3118,17 +3118,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>241975</t>
+          <t>241977</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>510492000001111001</t>
+          <t>510492000000387119</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>ABA CLEANING SERVICES LTD</t>
+          <t>AUTO MARKET PLACE LIMITED</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>360.0</v>
+        <v>400.0</v>
       </c>
       <c r="N38" t="n">
-        <v>360.0</v>
+        <v>400.0</v>
       </c>
       <c r="O38" t="n">
         <v>1.0</v>
@@ -3149,7 +3149,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>510492000001300001</t>
+          <t>510492000001316001</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3187,17 +3187,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>241977</t>
+          <t>241979</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>510492000000387119</t>
+          <t>510492000001064041</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>AUTO MARKET PLACE LIMITED</t>
+          <t>Jans Solutions Ltd</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>400.0</v>
+        <v>450.0</v>
       </c>
       <c r="N39" t="n">
-        <v>400.0</v>
+        <v>450.0</v>
       </c>
       <c r="O39" t="n">
         <v>1.0</v>
@@ -3218,7 +3218,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>510492000001316001</t>
+          <t>510492000001338033</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3256,17 +3256,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>241979</t>
+          <t>241986</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>510492000001064041</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Jans Solutions Ltd</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>450.0</v>
+        <v>238.8</v>
       </c>
       <c r="N40" t="n">
-        <v>450.0</v>
+        <v>238.8</v>
       </c>
       <c r="O40" t="n">
         <v>1.0</v>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>510492000001338033</t>
+          <t>510492000001338049</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3325,17 +3325,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>241986</t>
+          <t>241987</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3347,7 +3347,7 @@
         <v>238.8</v>
       </c>
       <c r="N41" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O41" t="n">
         <v>1.0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>510492000001338049</t>
+          <t>510492000001338066</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3394,17 +3394,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>241987</t>
+          <t>241988</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3416,7 +3416,7 @@
         <v>238.8</v>
       </c>
       <c r="N42" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="O42" t="n">
         <v>1.0</v>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>510492000001338066</t>
+          <t>510492000001338242</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3463,17 +3463,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>241988</t>
+          <t>241999</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N43" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O43" t="n">
         <v>1.0</v>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>510492000001338242</t>
+          <t>510492000001338338</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3532,17 +3532,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>241999</t>
+          <t>242005</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>510492000001338338</t>
+          <t>510492000001338370</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>242005</t>
+          <t>242007</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001144276</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>Creativa Ltd</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3632,7 +3632,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>510492000001338370</t>
+          <t>510492000001388001</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3670,17 +3670,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>242007</t>
+          <t>242021</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>510492000001144276</t>
+          <t>510492000001088061</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Creativa Ltd</t>
+          <t>Drive with Greta</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="N46" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="O46" t="n">
         <v>1.0</v>
@@ -3701,7 +3701,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>510492000001388001</t>
+          <t>510492000001391088</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3739,17 +3739,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>242021</t>
+          <t>242026</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>510492000001088061</t>
+          <t>510492000001391079</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Drive with Greta</t>
+          <t>NGS Plumbing &amp; Heating Ltd</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>360.0</v>
+        <v>75.0</v>
       </c>
       <c r="N47" t="n">
-        <v>360.0</v>
+        <v>75.0</v>
       </c>
       <c r="O47" t="n">
         <v>1.0</v>
@@ -3770,7 +3770,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>510492000001391088</t>
+          <t>510492000001403010</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3790,12 +3790,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3808,17 +3808,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>242026</t>
+          <t>242027</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>510492000001391079</t>
+          <t>510492000001403001</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>NGS Plumbing &amp; Heating Ltd</t>
+          <t>Malvern Renovation</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>75.0</v>
+        <v>120.0</v>
       </c>
       <c r="N48" t="n">
-        <v>75.0</v>
+        <v>120.0</v>
       </c>
       <c r="O48" t="n">
         <v>1.0</v>
@@ -3839,7 +3839,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>510492000001403010</t>
+          <t>510492000001417001</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3877,17 +3877,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>242027</t>
+          <t>242032</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>510492000001403001</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Malvern Renovation</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>120.0</v>
+        <v>238.8</v>
       </c>
       <c r="N49" t="n">
-        <v>120.0</v>
+        <v>238.8</v>
       </c>
       <c r="O49" t="n">
         <v>1.0</v>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>510492000001417001</t>
+          <t>510492000001417033</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3946,17 +3946,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>242032</t>
+          <t>242034</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>510492000001417033</t>
+          <t>510492000001417049</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4015,17 +4015,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>242034</t>
+          <t>242035</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="N51" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O51" t="n">
         <v>1.0</v>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>510492000001417049</t>
+          <t>510492000001417066</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4084,17 +4084,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>242035</t>
+          <t>242036</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="N52" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="O52" t="n">
         <v>1.0</v>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>510492000001417066</t>
+          <t>510492000001417242</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4153,17 +4153,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>242036</t>
+          <t>242047</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N53" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O53" t="n">
         <v>1.0</v>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>510492000001417242</t>
+          <t>510492000001417338</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4222,17 +4222,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>242047</t>
+          <t>242053</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4253,7 +4253,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>510492000001417338</t>
+          <t>510492000001445029</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>242053</t>
+          <t>242065</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001445020</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>BORN FOR IT LTD</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>240.0</v>
+        <v>660.0</v>
       </c>
       <c r="N55" t="n">
-        <v>240.0</v>
+        <v>660.0</v>
       </c>
       <c r="O55" t="n">
         <v>1.0</v>
@@ -4322,7 +4322,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>510492000001445029</t>
+          <t>510492000001450025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4356,21 +4356,21 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>242065</t>
+          <t>242068</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>510492000001445020</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>BORN FOR IT LTD</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>660.0</v>
+        <v>718.8</v>
       </c>
       <c r="N56" t="n">
-        <v>660.0</v>
+        <v>718.8</v>
       </c>
       <c r="O56" t="n">
         <v>1.0</v>
@@ -4391,7 +4391,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>510492000001450025</t>
+          <t>510492000001460089</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4425,21 +4425,21 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>242068</t>
+          <t>242075</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000639001</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>De'Osa Engineering Services</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4448,10 +4448,10 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>718.8</v>
+        <v>120.0</v>
       </c>
       <c r="N57" t="n">
-        <v>718.8</v>
+        <v>120.0</v>
       </c>
       <c r="O57" t="n">
         <v>1.0</v>
@@ -4460,7 +4460,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>510492000001359025</t>
+          <t>510492000001460115</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4498,17 +4498,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>242012</t>
+          <t>242076</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>510492000000317525</t>
+          <t>510492000001460106</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>EAGLE PROPERTY CARE</t>
+          <t>MOUNTAINS OF GLORY</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>240.0</v>
+        <v>250.0</v>
       </c>
       <c r="N58" t="n">
-        <v>240.0</v>
+        <v>250.0</v>
       </c>
       <c r="O58" t="n">
         <v>1.0</v>
@@ -4529,7 +4529,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>510492000001460089</t>
+          <t>510492000001359025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4567,17 +4567,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>242075</t>
+          <t>242012</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>510492000000639001</t>
+          <t>510492000000317525</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>De'Osa Engineering Services</t>
+          <t>EAGLE PROPERTY CARE</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="N59" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="O59" t="n">
         <v>1.0</v>
@@ -4598,7 +4598,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>510492000001460115</t>
+          <t>510492000001460138</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>242076</t>
+          <t>242077</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>510492000001460106</t>
+          <t>510492000000386033</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>MOUNTAINS OF GLORY</t>
+          <t>ALPHA EUROPE LTD</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>250.0</v>
+        <v>240.0</v>
       </c>
       <c r="N60" t="n">
-        <v>250.0</v>
+        <v>240.0</v>
       </c>
       <c r="O60" t="n">
         <v>1.0</v>
@@ -4667,7 +4667,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>510492000001460138</t>
+          <t>510492000001482001</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4705,17 +4705,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>242077</t>
+          <t>242082</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>510492000000386033</t>
+          <t>510492000001057001</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>ALPHA EUROPE LTD</t>
+          <t>Corby Motors Ltd</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>240.0</v>
+        <v>55.0</v>
       </c>
       <c r="N61" t="n">
-        <v>240.0</v>
+        <v>555.0</v>
       </c>
       <c r="O61" t="n">
         <v>1.0</v>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>510492000001482001</t>
+          <t>510492000001482018</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4774,17 +4774,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>242082</t>
+          <t>242083</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>510492000001057001</t>
+          <t>510492000001413024</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Corby Motors Ltd</t>
+          <t>88 DRIVING SCHOOL LTD</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>55.0</v>
+        <v>110.0</v>
       </c>
       <c r="N62" t="n">
-        <v>555.0</v>
+        <v>110.0</v>
       </c>
       <c r="O62" t="n">
         <v>1.0</v>
@@ -4805,7 +4805,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>510492000001482018</t>
+          <t>510492000001486010</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4843,17 +4843,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>242083</t>
+          <t>242085</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>510492000001413024</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>88 DRIVING SCHOOL LTD</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>110.0</v>
+        <v>238.8</v>
       </c>
       <c r="N63" t="n">
-        <v>110.0</v>
+        <v>238.8</v>
       </c>
       <c r="O63" t="n">
         <v>1.0</v>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>510492000001486010</t>
+          <t>510492000001486042</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4912,17 +4912,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>242085</t>
+          <t>242087</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>510492000001486042</t>
+          <t>510492000001486058</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>242087</t>
+          <t>242088</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="N65" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O65" t="n">
         <v>1.0</v>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>510492000001486058</t>
+          <t>510492000001486075</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5050,17 +5050,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>242088</t>
+          <t>242089</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="N66" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="O66" t="n">
         <v>1.0</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>510492000001486075</t>
+          <t>510492000001486171</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5119,17 +5119,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>242089</t>
+          <t>242095</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000505059</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>Chorus Music Therapy &amp; Education</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="N67" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="O67" t="n">
         <v>1.0</v>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>510492000001486171</t>
+          <t>510492000001486347</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5188,17 +5188,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>242095</t>
+          <t>242106</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>510492000000505059</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Chorus Music Therapy &amp; Education</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="N68" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="O68" t="n">
         <v>1.0</v>
@@ -5219,7 +5219,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>510492000001486347</t>
+          <t>510492000001496109</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5257,17 +5257,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>242106</t>
+          <t>242114</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001378001</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>240.0</v>
+        <v>270.0</v>
       </c>
       <c r="N69" t="n">
-        <v>240.0</v>
+        <v>270.0</v>
       </c>
       <c r="O69" t="n">
         <v>1.0</v>
@@ -5288,7 +5288,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>510492000001496109</t>
+          <t>510492000001517010</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>242114</t>
+          <t>242120</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>510492000001378001</t>
+          <t>510492000001517001</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
+          <t>Max Out Tutoring</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>270.0</v>
+        <v>120.0</v>
       </c>
       <c r="N70" t="n">
-        <v>270.0</v>
+        <v>480.0</v>
       </c>
       <c r="O70" t="n">
         <v>1.0</v>
@@ -5357,7 +5357,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>510492000001510042</t>
+          <t>510492000001517029</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5395,17 +5395,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>242118</t>
+          <t>242121</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>510492000001488006</t>
+          <t>510492000001517001</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>SPOT CLEANERS LTD</t>
+          <t>Max Out Tutoring</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>130.0</v>
+        <v>480.0</v>
       </c>
       <c r="N71" t="n">
-        <v>130.0</v>
+        <v>480.0</v>
       </c>
       <c r="O71" t="n">
         <v>1.0</v>
@@ -5426,7 +5426,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>510492000001517010</t>
+          <t>510492000001517056</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5464,17 +5464,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>242120</t>
+          <t>242122</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>510492000001517001</t>
+          <t>510492000001088061</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Max Out Tutoring</t>
+          <t>Drive with Greta</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>120.0</v>
+        <v>28.8</v>
       </c>
       <c r="N72" t="n">
-        <v>480.0</v>
+        <v>28.8</v>
       </c>
       <c r="O72" t="n">
         <v>1.0</v>
@@ -5495,7 +5495,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>510492000001517029</t>
+          <t>510492000001517086</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5533,17 +5533,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>242121</t>
+          <t>242124</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>510492000001517001</t>
+          <t>510492000001260001</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Max Out Tutoring</t>
+          <t>Elite Learning Epsom Ltd</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>480.0</v>
+        <v>57.24</v>
       </c>
       <c r="N73" t="n">
-        <v>480.0</v>
+        <v>57.24</v>
       </c>
       <c r="O73" t="n">
         <v>1.0</v>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>510492000001517056</t>
+          <t>510492000001517128</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5602,17 +5602,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>242122</t>
+          <t>242127</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>510492000001088061</t>
+          <t>510492000001025001</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Drive with Greta</t>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5621,10 +5621,10 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>28.8</v>
+        <v>125.0</v>
       </c>
       <c r="N74" t="n">
-        <v>28.8</v>
+        <v>375.0</v>
       </c>
       <c r="O74" t="n">
         <v>1.0</v>
@@ -5633,7 +5633,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>510492000001517086</t>
+          <t>510492000001527001</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5671,17 +5671,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>242124</t>
+          <t>242128</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>510492000001260001</t>
+          <t>510492000000256001</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Elite Learning Epsom Ltd</t>
+          <t>OPTIMUM GLOBAL LINKS</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5690,155 +5690,17 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>57.24</v>
+        <v>70.0</v>
       </c>
       <c r="N75" t="n">
-        <v>57.24</v>
+        <v>120.0</v>
       </c>
       <c r="O75" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>510492000001517128</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H76" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>242127</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>510492000001025001</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M76" t="n">
-        <v>125.0</v>
-      </c>
-      <c r="N76" t="n">
-        <v>375.0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>510492000001527001</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H77" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>242128</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>510492000000256001</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>OPTIMUM GLOBAL LINKS</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M77" t="n">
-        <v>120.0</v>
-      </c>
-      <c r="N77" t="n">
-        <v>120.0</v>
-      </c>
-      <c r="O77" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="55" t="inlineStr">
+      <c r="A76" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5847,7 +5709,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A78:O78"/>
+    <mergeCell ref="A76:O76"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_overdue_zoho.xlsx
+++ b/AR_overdue_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O76"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 25/09/2026</t>
+As of 05/10/2026</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>359</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>319</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>303</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>303</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>241</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>241</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>238</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>238</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>225</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>219</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>213</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>213</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>211</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>211</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>211</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>211</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>510492000001231242</t>
+          <t>510492000001231370</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2566,17 +2566,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>241925</t>
+          <t>241933</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000001079001</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>RBD Driving School</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>240.0</v>
+        <v>200.0</v>
       </c>
       <c r="N30" t="n">
-        <v>240.0</v>
+        <v>200.0</v>
       </c>
       <c r="O30" t="n">
         <v>1.0</v>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>510492000001231370</t>
+          <t>510492000001231386</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2635,17 +2635,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>241933</t>
+          <t>241934</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>510492000001079001</t>
+          <t>510492000001144276</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>RBD Driving School</t>
+          <t>Creativa Ltd</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>200.0</v>
+        <v>240.0</v>
       </c>
       <c r="N31" t="n">
-        <v>200.0</v>
+        <v>240.0</v>
       </c>
       <c r="O31" t="n">
         <v>1.0</v>
@@ -2666,7 +2666,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>510492000001231386</t>
+          <t>510492000001279033</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2686,12 +2686,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>121</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2700,21 +2700,21 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>241934</t>
+          <t>241949</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>510492000001144276</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Creativa Ltd</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>240.0</v>
+        <v>216.4</v>
       </c>
       <c r="N32" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="O32" t="n">
         <v>1.0</v>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>510492000001279033</t>
+          <t>510492000001279066</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>121</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2773,17 +2773,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>241949</t>
+          <t>241951</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>216.4</v>
+        <v>238.8</v>
       </c>
       <c r="N33" t="n">
         <v>238.8</v>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>510492000001279066</t>
+          <t>510492000001279242</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>121</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>241951</t>
+          <t>241962</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>238.8</v>
+        <v>230.0</v>
       </c>
       <c r="N34" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O34" t="n">
         <v>1.0</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>510492000001279242</t>
+          <t>510492000001279370</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>121</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2911,17 +2911,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>241962</t>
+          <t>241970</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000001144276</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Creativa Ltd</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2942,7 +2942,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>510492000001279370</t>
+          <t>510492000001288131</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2980,17 +2980,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>241970</t>
+          <t>241975</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>510492000001144276</t>
+          <t>510492000001111001</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Creativa Ltd</t>
+          <t>ABA CLEANING SERVICES LTD</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="N36" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="O36" t="n">
         <v>1.0</v>
@@ -3011,7 +3011,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>510492000001288131</t>
+          <t>510492000001300001</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3031,12 +3031,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3049,17 +3049,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>241975</t>
+          <t>241977</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>510492000001111001</t>
+          <t>510492000000387119</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>ABA CLEANING SERVICES LTD</t>
+          <t>AUTO MARKET PLACE LIMITED</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>360.0</v>
+        <v>400.0</v>
       </c>
       <c r="N37" t="n">
-        <v>360.0</v>
+        <v>400.0</v>
       </c>
       <c r="O37" t="n">
         <v>1.0</v>
@@ -3080,7 +3080,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>510492000001300001</t>
+          <t>510492000001316001</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3118,17 +3118,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>241977</t>
+          <t>241979</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>510492000000387119</t>
+          <t>510492000001064041</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>AUTO MARKET PLACE LIMITED</t>
+          <t>Jans Solutions Ltd</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>400.0</v>
+        <v>450.0</v>
       </c>
       <c r="N38" t="n">
-        <v>400.0</v>
+        <v>450.0</v>
       </c>
       <c r="O38" t="n">
         <v>1.0</v>
@@ -3149,7 +3149,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>510492000001316001</t>
+          <t>510492000001338033</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>91</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3187,17 +3187,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>241979</t>
+          <t>241986</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>510492000001064041</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Jans Solutions Ltd</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>450.0</v>
+        <v>238.8</v>
       </c>
       <c r="N39" t="n">
-        <v>450.0</v>
+        <v>238.8</v>
       </c>
       <c r="O39" t="n">
         <v>1.0</v>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>510492000001338033</t>
+          <t>510492000001338049</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>91</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3256,17 +3256,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>241986</t>
+          <t>241987</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3278,7 +3278,7 @@
         <v>238.8</v>
       </c>
       <c r="N40" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O40" t="n">
         <v>1.0</v>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>510492000001338049</t>
+          <t>510492000001338066</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>91</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3325,17 +3325,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>241987</t>
+          <t>241988</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3347,7 +3347,7 @@
         <v>238.8</v>
       </c>
       <c r="N41" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="O41" t="n">
         <v>1.0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>510492000001338066</t>
+          <t>510492000001338242</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>91</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3394,17 +3394,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>241988</t>
+          <t>241999</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N42" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O42" t="n">
         <v>1.0</v>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>510492000001338242</t>
+          <t>510492000001338338</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>91</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3463,17 +3463,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>241999</t>
+          <t>242005</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>510492000001338338</t>
+          <t>510492000001338370</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>91</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3532,17 +3532,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>242005</t>
+          <t>242007</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001144276</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>Creativa Ltd</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3563,7 +3563,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>510492000001338370</t>
+          <t>510492000001388001</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3583,12 +3583,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>242007</t>
+          <t>242021</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>510492000001144276</t>
+          <t>510492000001088061</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Creativa Ltd</t>
+          <t>Drive with Greta</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="N45" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="O45" t="n">
         <v>1.0</v>
@@ -3632,7 +3632,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>510492000001388001</t>
+          <t>510492000001391088</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3670,17 +3670,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>242021</t>
+          <t>242026</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>510492000001088061</t>
+          <t>510492000001391079</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Drive with Greta</t>
+          <t>NGS Plumbing &amp; Heating Ltd</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>360.0</v>
+        <v>75.0</v>
       </c>
       <c r="N46" t="n">
-        <v>360.0</v>
+        <v>75.0</v>
       </c>
       <c r="O46" t="n">
         <v>1.0</v>
@@ -3701,7 +3701,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>510492000001391088</t>
+          <t>510492000001403010</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3739,17 +3739,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>242026</t>
+          <t>242027</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>510492000001391079</t>
+          <t>510492000001403001</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>NGS Plumbing &amp; Heating Ltd</t>
+          <t>Malvern Renovation</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>75.0</v>
+        <v>120.0</v>
       </c>
       <c r="N47" t="n">
-        <v>75.0</v>
+        <v>120.0</v>
       </c>
       <c r="O47" t="n">
         <v>1.0</v>
@@ -3770,7 +3770,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>510492000001403010</t>
+          <t>510492000001417001</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3790,12 +3790,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3808,17 +3808,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>242027</t>
+          <t>242032</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>510492000001403001</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Malvern Renovation</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>120.0</v>
+        <v>238.8</v>
       </c>
       <c r="N48" t="n">
-        <v>120.0</v>
+        <v>238.8</v>
       </c>
       <c r="O48" t="n">
         <v>1.0</v>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>510492000001417001</t>
+          <t>510492000001417033</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3877,17 +3877,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>242032</t>
+          <t>242034</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>510492000001417033</t>
+          <t>510492000001417049</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3946,17 +3946,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>242034</t>
+          <t>242035</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="N50" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O50" t="n">
         <v>1.0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>510492000001417049</t>
+          <t>510492000001417066</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4015,17 +4015,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>242035</t>
+          <t>242036</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="N51" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="O51" t="n">
         <v>1.0</v>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>510492000001417066</t>
+          <t>510492000001417242</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4084,17 +4084,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>242036</t>
+          <t>242047</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N52" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O52" t="n">
         <v>1.0</v>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>510492000001417242</t>
+          <t>510492000001417338</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4153,17 +4153,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>242047</t>
+          <t>242053</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4184,7 +4184,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>510492000001417338</t>
+          <t>510492000001445029</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4222,17 +4222,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>242053</t>
+          <t>242065</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001445020</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>BORN FOR IT LTD</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>240.0</v>
+        <v>660.0</v>
       </c>
       <c r="N54" t="n">
-        <v>240.0</v>
+        <v>660.0</v>
       </c>
       <c r="O54" t="n">
         <v>1.0</v>
@@ -4253,7 +4253,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>510492000001445029</t>
+          <t>510492000001450025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4287,21 +4287,21 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>242065</t>
+          <t>242068</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>510492000001445020</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>BORN FOR IT LTD</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>660.0</v>
+        <v>718.8</v>
       </c>
       <c r="N55" t="n">
-        <v>660.0</v>
+        <v>718.8</v>
       </c>
       <c r="O55" t="n">
         <v>1.0</v>
@@ -4322,7 +4322,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>510492000001450025</t>
+          <t>510492000001460089</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4356,21 +4356,21 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>242068</t>
+          <t>242075</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000639001</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>De'Osa Engineering Services</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>718.8</v>
+        <v>120.0</v>
       </c>
       <c r="N56" t="n">
-        <v>718.8</v>
+        <v>120.0</v>
       </c>
       <c r="O56" t="n">
         <v>1.0</v>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>510492000001460089</t>
+          <t>510492000001460115</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4429,17 +4429,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>242075</t>
+          <t>242076</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>510492000000639001</t>
+          <t>510492000001460106</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>De'Osa Engineering Services</t>
+          <t>MOUNTAINS OF GLORY</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4448,10 +4448,10 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>120.0</v>
+        <v>250.0</v>
       </c>
       <c r="N57" t="n">
-        <v>120.0</v>
+        <v>250.0</v>
       </c>
       <c r="O57" t="n">
         <v>1.0</v>
@@ -4460,7 +4460,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>510492000001460115</t>
+          <t>510492000001460138</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4498,17 +4498,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>242076</t>
+          <t>242077</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>510492000001460106</t>
+          <t>510492000000386033</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>MOUNTAINS OF GLORY</t>
+          <t>ALPHA EUROPE LTD</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>250.0</v>
+        <v>240.0</v>
       </c>
       <c r="N58" t="n">
-        <v>250.0</v>
+        <v>240.0</v>
       </c>
       <c r="O58" t="n">
         <v>1.0</v>
@@ -4529,7 +4529,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>510492000001359025</t>
+          <t>510492000001482001</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4567,17 +4567,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>242012</t>
+          <t>242082</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>510492000000317525</t>
+          <t>510492000001057001</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>EAGLE PROPERTY CARE</t>
+          <t>Corby Motors Ltd</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>240.0</v>
+        <v>55.0</v>
       </c>
       <c r="N59" t="n">
-        <v>240.0</v>
+        <v>555.0</v>
       </c>
       <c r="O59" t="n">
         <v>1.0</v>
@@ -4598,7 +4598,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>510492000001460138</t>
+          <t>510492000001482018</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>242077</t>
+          <t>242083</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>510492000000386033</t>
+          <t>510492000001413024</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>ALPHA EUROPE LTD</t>
+          <t>88 DRIVING SCHOOL LTD</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>240.0</v>
+        <v>110.0</v>
       </c>
       <c r="N60" t="n">
-        <v>240.0</v>
+        <v>110.0</v>
       </c>
       <c r="O60" t="n">
         <v>1.0</v>
@@ -4667,7 +4667,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>510492000001482001</t>
+          <t>510492000001359025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4705,17 +4705,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>242082</t>
+          <t>242012</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>510492000001057001</t>
+          <t>510492000000317525</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Corby Motors Ltd</t>
+          <t>EAGLE PROPERTY CARE</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>55.0</v>
+        <v>240.0</v>
       </c>
       <c r="N61" t="n">
-        <v>555.0</v>
+        <v>240.0</v>
       </c>
       <c r="O61" t="n">
         <v>1.0</v>
@@ -4736,7 +4736,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>510492000001482018</t>
+          <t>510492000001486010</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4774,17 +4774,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>242083</t>
+          <t>242085</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>510492000001413024</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>88 DRIVING SCHOOL LTD</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>110.0</v>
+        <v>238.8</v>
       </c>
       <c r="N62" t="n">
-        <v>110.0</v>
+        <v>238.8</v>
       </c>
       <c r="O62" t="n">
         <v>1.0</v>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>510492000001486010</t>
+          <t>510492000001486042</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4843,17 +4843,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>242085</t>
+          <t>242087</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>510492000001486042</t>
+          <t>510492000001486058</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4912,17 +4912,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>242087</t>
+          <t>242088</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="N64" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O64" t="n">
         <v>1.0</v>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>510492000001486058</t>
+          <t>510492000001486075</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>242088</t>
+          <t>242089</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="N65" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="O65" t="n">
         <v>1.0</v>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>510492000001486075</t>
+          <t>510492000001486171</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5050,17 +5050,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>242089</t>
+          <t>242095</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000505059</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>Chorus Music Therapy &amp; Education</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="N66" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="O66" t="n">
         <v>1.0</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>510492000001486171</t>
+          <t>510492000001486347</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5119,17 +5119,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>242095</t>
+          <t>242106</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>510492000000505059</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Chorus Music Therapy &amp; Education</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="N67" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="O67" t="n">
         <v>1.0</v>
@@ -5150,7 +5150,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>510492000001486347</t>
+          <t>510492000001496109</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5188,17 +5188,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>242106</t>
+          <t>242114</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001378001</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>240.0</v>
+        <v>270.0</v>
       </c>
       <c r="N68" t="n">
-        <v>240.0</v>
+        <v>270.0</v>
       </c>
       <c r="O68" t="n">
         <v>1.0</v>
@@ -5219,7 +5219,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>510492000001496109</t>
+          <t>510492000001517029</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5257,17 +5257,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>242114</t>
+          <t>242121</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>510492000001378001</t>
+          <t>510492000001517001</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
+          <t>Max Out Tutoring</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>270.0</v>
+        <v>360.0</v>
       </c>
       <c r="N69" t="n">
-        <v>270.0</v>
+        <v>480.0</v>
       </c>
       <c r="O69" t="n">
         <v>1.0</v>
@@ -5288,7 +5288,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>510492000001517010</t>
+          <t>510492000001517056</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>242120</t>
+          <t>242122</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>510492000001517001</t>
+          <t>510492000001088061</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Max Out Tutoring</t>
+          <t>Drive with Greta</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>120.0</v>
+        <v>28.8</v>
       </c>
       <c r="N70" t="n">
-        <v>480.0</v>
+        <v>28.8</v>
       </c>
       <c r="O70" t="n">
         <v>1.0</v>
@@ -5357,7 +5357,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>510492000001517029</t>
+          <t>510492000001517086</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5395,17 +5395,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>242121</t>
+          <t>242124</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>510492000001517001</t>
+          <t>510492000001260001</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Max Out Tutoring</t>
+          <t>Elite Learning Epsom Ltd</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>480.0</v>
+        <v>57.24</v>
       </c>
       <c r="N71" t="n">
-        <v>480.0</v>
+        <v>57.24</v>
       </c>
       <c r="O71" t="n">
         <v>1.0</v>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>510492000001517056</t>
+          <t>510492000001517128</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5464,17 +5464,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>242122</t>
+          <t>242127</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>510492000001088061</t>
+          <t>510492000001025001</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Drive with Greta</t>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>28.8</v>
+        <v>125.0</v>
       </c>
       <c r="N72" t="n">
-        <v>28.8</v>
+        <v>375.0</v>
       </c>
       <c r="O72" t="n">
         <v>1.0</v>
@@ -5495,7 +5495,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>510492000001517086</t>
+          <t>510492000001527001</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5533,17 +5533,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>242124</t>
+          <t>242128</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>510492000001260001</t>
+          <t>510492000000256001</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Elite Learning Epsom Ltd</t>
+          <t>OPTIMUM GLOBAL LINKS</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>57.24</v>
+        <v>70.0</v>
       </c>
       <c r="N73" t="n">
-        <v>57.24</v>
+        <v>120.0</v>
       </c>
       <c r="O73" t="n">
         <v>1.0</v>
@@ -5564,7 +5564,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>510492000001517128</t>
+          <t>510492000001543036</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5602,17 +5602,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>242127</t>
+          <t>242133</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>510492000001025001</t>
+          <t>510492000001543027</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+          <t>MRB ELITE PROTECTION &amp; MAINTENANCE LTD</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5621,10 +5621,10 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>125.0</v>
+        <v>420.0</v>
       </c>
       <c r="N74" t="n">
-        <v>375.0</v>
+        <v>420.0</v>
       </c>
       <c r="O74" t="n">
         <v>1.0</v>
@@ -5633,7 +5633,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>510492000001527001</t>
+          <t>510492000001561010</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5671,17 +5671,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>242128</t>
+          <t>242136</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>510492000000256001</t>
+          <t>510492000001561001</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>OPTIMUM GLOBAL LINKS</t>
+          <t>BURTON DRIVING SCHOOL LTD</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5690,17 +5690,86 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>70.0</v>
+        <v>300.0</v>
       </c>
       <c r="N75" t="n">
-        <v>120.0</v>
+        <v>300.0</v>
       </c>
       <c r="O75" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="55" t="inlineStr">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>510492000001564010</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>242137</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>510492000001564001</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Stabilus Safety GmbH</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>780.0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>780.0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5709,7 +5778,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A76:O76"/>
+    <mergeCell ref="A77:O77"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_overdue_zoho.xlsx
+++ b/AR_overdue_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 05/10/2026</t>
+As of 07/10/2026</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>361</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>321</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>305</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>305</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>274</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>274</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>274</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>243</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>243</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>240</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>240</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>227</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>221</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>215</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>215</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>213</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>213</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>213</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>213</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>203</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>105</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>510492000001417001</t>
+          <t>510492000001417033</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3808,17 +3808,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>242032</t>
+          <t>242034</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>510492000001417033</t>
+          <t>510492000001417049</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3877,17 +3877,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>242034</t>
+          <t>242035</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="N49" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O49" t="n">
         <v>1.0</v>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>510492000001417049</t>
+          <t>510492000001417066</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3946,17 +3946,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>242035</t>
+          <t>242036</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="N50" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="O50" t="n">
         <v>1.0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>510492000001417066</t>
+          <t>510492000001417242</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4015,17 +4015,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>242036</t>
+          <t>242047</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N51" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O51" t="n">
         <v>1.0</v>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>510492000001417242</t>
+          <t>510492000001417338</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4084,17 +4084,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>242047</t>
+          <t>242053</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4115,7 +4115,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>510492000001417338</t>
+          <t>510492000001445029</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4153,17 +4153,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>242053</t>
+          <t>242065</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001445020</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>BORN FOR IT LTD</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>240.0</v>
+        <v>660.0</v>
       </c>
       <c r="N53" t="n">
-        <v>240.0</v>
+        <v>660.0</v>
       </c>
       <c r="O53" t="n">
         <v>1.0</v>
@@ -4184,7 +4184,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>510492000001445029</t>
+          <t>510492000001359025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4222,17 +4222,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>242065</t>
+          <t>242012</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>510492000001445020</t>
+          <t>510492000000317525</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>BORN FOR IT LTD</t>
+          <t>EAGLE PROPERTY CARE</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>660.0</v>
+        <v>240.0</v>
       </c>
       <c r="N54" t="n">
-        <v>660.0</v>
+        <v>240.0</v>
       </c>
       <c r="O54" t="n">
         <v>1.0</v>
@@ -4253,7 +4253,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>510492000001450025</t>
+          <t>510492000001460089</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4287,21 +4287,21 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>242068</t>
+          <t>242075</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000639001</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>De'Osa Engineering Services</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>718.8</v>
+        <v>120.0</v>
       </c>
       <c r="N55" t="n">
-        <v>718.8</v>
+        <v>120.0</v>
       </c>
       <c r="O55" t="n">
         <v>1.0</v>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>510492000001460089</t>
+          <t>510492000001460115</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4360,17 +4360,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>242075</t>
+          <t>242076</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>510492000000639001</t>
+          <t>510492000001460106</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>De'Osa Engineering Services</t>
+          <t>MOUNTAINS OF GLORY</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>120.0</v>
+        <v>250.0</v>
       </c>
       <c r="N56" t="n">
-        <v>120.0</v>
+        <v>250.0</v>
       </c>
       <c r="O56" t="n">
         <v>1.0</v>
@@ -4391,7 +4391,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>510492000001460115</t>
+          <t>510492000001460138</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4429,17 +4429,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>242076</t>
+          <t>242077</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>510492000001460106</t>
+          <t>510492000000386033</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>MOUNTAINS OF GLORY</t>
+          <t>ALPHA EUROPE LTD</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4448,10 +4448,10 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>250.0</v>
+        <v>240.0</v>
       </c>
       <c r="N57" t="n">
-        <v>250.0</v>
+        <v>240.0</v>
       </c>
       <c r="O57" t="n">
         <v>1.0</v>
@@ -4460,7 +4460,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>510492000001460138</t>
+          <t>510492000001482001</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4498,17 +4498,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>242077</t>
+          <t>242082</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>510492000000386033</t>
+          <t>510492000001057001</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>ALPHA EUROPE LTD</t>
+          <t>Corby Motors Ltd</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>240.0</v>
+        <v>55.0</v>
       </c>
       <c r="N58" t="n">
-        <v>240.0</v>
+        <v>555.0</v>
       </c>
       <c r="O58" t="n">
         <v>1.0</v>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>510492000001482001</t>
+          <t>510492000001482018</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4567,17 +4567,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>242082</t>
+          <t>242083</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>510492000001057001</t>
+          <t>510492000001413024</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Corby Motors Ltd</t>
+          <t>88 DRIVING SCHOOL LTD</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>55.0</v>
+        <v>110.0</v>
       </c>
       <c r="N59" t="n">
-        <v>555.0</v>
+        <v>110.0</v>
       </c>
       <c r="O59" t="n">
         <v>1.0</v>
@@ -4598,7 +4598,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>510492000001482018</t>
+          <t>510492000001486010</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>242083</t>
+          <t>242085</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>510492000001413024</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>88 DRIVING SCHOOL LTD</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>110.0</v>
+        <v>238.8</v>
       </c>
       <c r="N60" t="n">
-        <v>110.0</v>
+        <v>238.8</v>
       </c>
       <c r="O60" t="n">
         <v>1.0</v>
@@ -4667,7 +4667,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>510492000001359025</t>
+          <t>510492000001486042</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4705,17 +4705,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>242012</t>
+          <t>242087</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>510492000000317525</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>EAGLE PROPERTY CARE</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="N61" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="O61" t="n">
         <v>1.0</v>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>510492000001486010</t>
+          <t>510492000001486058</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4774,17 +4774,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>242085</t>
+          <t>242088</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="N62" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O62" t="n">
         <v>1.0</v>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>510492000001486042</t>
+          <t>510492000001486075</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4843,17 +4843,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>242087</t>
+          <t>242089</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>510492000001486058</t>
+          <t>510492000001486171</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4912,17 +4912,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>242088</t>
+          <t>242095</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000505059</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>Chorus Music Therapy &amp; Education</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>477.6</v>
+        <v>120.0</v>
       </c>
       <c r="N64" t="n">
-        <v>477.6</v>
+        <v>120.0</v>
       </c>
       <c r="O64" t="n">
         <v>1.0</v>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>510492000001486075</t>
+          <t>510492000001486347</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>242089</t>
+          <t>242106</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N65" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O65" t="n">
         <v>1.0</v>
@@ -5012,7 +5012,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>510492000001486171</t>
+          <t>510492000001496109</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5050,17 +5050,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>242095</t>
+          <t>242114</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>510492000000505059</t>
+          <t>510492000001378001</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Chorus Music Therapy &amp; Education</t>
+          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>120.0</v>
+        <v>270.0</v>
       </c>
       <c r="N66" t="n">
-        <v>120.0</v>
+        <v>270.0</v>
       </c>
       <c r="O66" t="n">
         <v>1.0</v>
@@ -5081,7 +5081,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>510492000001486347</t>
+          <t>510492000001517029</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5119,17 +5119,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>242106</t>
+          <t>242121</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001517001</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>Max Out Tutoring</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="N67" t="n">
-        <v>240.0</v>
+        <v>480.0</v>
       </c>
       <c r="O67" t="n">
         <v>1.0</v>
@@ -5150,7 +5150,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>510492000001496109</t>
+          <t>510492000001517056</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5188,17 +5188,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>242114</t>
+          <t>242122</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>510492000001378001</t>
+          <t>510492000001088061</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
+          <t>Drive with Greta</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>270.0</v>
+        <v>28.8</v>
       </c>
       <c r="N68" t="n">
-        <v>270.0</v>
+        <v>28.8</v>
       </c>
       <c r="O68" t="n">
         <v>1.0</v>
@@ -5219,7 +5219,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>510492000001517029</t>
+          <t>510492000001517086</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5257,17 +5257,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>242121</t>
+          <t>242124</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>510492000001517001</t>
+          <t>510492000001260001</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Max Out Tutoring</t>
+          <t>Elite Learning Epsom Ltd</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>360.0</v>
+        <v>57.24</v>
       </c>
       <c r="N69" t="n">
-        <v>480.0</v>
+        <v>57.24</v>
       </c>
       <c r="O69" t="n">
         <v>1.0</v>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>510492000001517056</t>
+          <t>510492000001517128</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>242122</t>
+          <t>242127</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>510492000001088061</t>
+          <t>510492000001025001</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Drive with Greta</t>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>28.8</v>
+        <v>125.0</v>
       </c>
       <c r="N70" t="n">
-        <v>28.8</v>
+        <v>375.0</v>
       </c>
       <c r="O70" t="n">
         <v>1.0</v>
@@ -5357,7 +5357,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>510492000001517086</t>
+          <t>510492000001527001</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5395,17 +5395,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>242124</t>
+          <t>242128</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>510492000001260001</t>
+          <t>510492000000256001</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Elite Learning Epsom Ltd</t>
+          <t>OPTIMUM GLOBAL LINKS</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>57.24</v>
+        <v>70.0</v>
       </c>
       <c r="N71" t="n">
-        <v>57.24</v>
+        <v>120.0</v>
       </c>
       <c r="O71" t="n">
         <v>1.0</v>
@@ -5426,7 +5426,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>510492000001517128</t>
+          <t>510492000001543036</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5464,17 +5464,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>242127</t>
+          <t>242133</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>510492000001025001</t>
+          <t>510492000001543027</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+          <t>MRB ELITE PROTECTION &amp; MAINTENANCE LTD</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>125.0</v>
+        <v>420.0</v>
       </c>
       <c r="N72" t="n">
-        <v>375.0</v>
+        <v>420.0</v>
       </c>
       <c r="O72" t="n">
         <v>1.0</v>
@@ -5495,7 +5495,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>510492000001527001</t>
+          <t>510492000001561010</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5533,17 +5533,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>242128</t>
+          <t>242136</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>510492000000256001</t>
+          <t>510492000001561001</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>OPTIMUM GLOBAL LINKS</t>
+          <t>BURTON DRIVING SCHOOL LTD</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>70.0</v>
+        <v>300.0</v>
       </c>
       <c r="N73" t="n">
-        <v>120.0</v>
+        <v>300.0</v>
       </c>
       <c r="O73" t="n">
         <v>1.0</v>
@@ -5564,7 +5564,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>510492000001543036</t>
+          <t>510492000001564010</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5602,17 +5602,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>242133</t>
+          <t>242137</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>510492000001543027</t>
+          <t>510492000001564001</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>MRB ELITE PROTECTION &amp; MAINTENANCE LTD</t>
+          <t>Stabilus Safety GmbH</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5621,10 +5621,10 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>420.0</v>
+        <v>780.0</v>
       </c>
       <c r="N74" t="n">
-        <v>420.0</v>
+        <v>780.0</v>
       </c>
       <c r="O74" t="n">
         <v>1.0</v>
@@ -5633,7 +5633,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>510492000001561010</t>
+          <t>510492000001566001</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5671,17 +5671,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>242136</t>
+          <t>242138</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>510492000001561001</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>BURTON DRIVING SCHOOL LTD</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5690,10 +5690,10 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>300.0</v>
+        <v>238.8</v>
       </c>
       <c r="N75" t="n">
-        <v>300.0</v>
+        <v>238.8</v>
       </c>
       <c r="O75" t="n">
         <v>1.0</v>
@@ -5702,7 +5702,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>510492000001564010</t>
+          <t>510492000001566037</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5740,17 +5740,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>242137</t>
+          <t>242140</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>510492000001564001</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Stabilus Safety GmbH</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5759,17 +5759,362 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>780.0</v>
+        <v>238.8</v>
       </c>
       <c r="N76" t="n">
-        <v>780.0</v>
+        <v>238.8</v>
       </c>
       <c r="O76" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="55" t="inlineStr">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>510492000001566055</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>242141</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>510492000000123277</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Patrick Shoes Limited</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>477.6</v>
+      </c>
+      <c r="N77" t="n">
+        <v>477.6</v>
+      </c>
+      <c r="O77" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>510492000001566074</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>242142</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>510492000000192073</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>SUPERHOUSE (UK) LIMITED</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="N78" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>510492000001566182</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>242148</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>510492000000505059</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Chorus Music Therapy &amp; Education</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>510492000001566254</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>242152</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>510492000000742001</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Adam’s Painting and Decorating</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>510492000001566380</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>242159</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>510492000000123277</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Patrick Shoes Limited</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5778,7 +6123,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A77:O77"/>
+    <mergeCell ref="A82:O82"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_overdue_zoho.xlsx
+++ b/AR_overdue_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O82"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 07/10/2026</t>
+As of 09/10/2026</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>363</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>323</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>307</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>307</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>276</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>276</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>276</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>245</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>245</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>242</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>242</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>229</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>223</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>217</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>217</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>215</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>215</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>215</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>215</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>156</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>156</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>156</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>156</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>117</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>510492000001486171</t>
+          <t>510492000001486347</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4912,17 +4912,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>242095</t>
+          <t>242106</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>510492000000505059</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Chorus Music Therapy &amp; Education</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="N64" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="O64" t="n">
         <v>1.0</v>
@@ -4943,7 +4943,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>510492000001486347</t>
+          <t>510492000001496109</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>242106</t>
+          <t>242114</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001378001</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>240.0</v>
+        <v>270.0</v>
       </c>
       <c r="N65" t="n">
-        <v>240.0</v>
+        <v>270.0</v>
       </c>
       <c r="O65" t="n">
         <v>1.0</v>
@@ -5012,7 +5012,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>510492000001496109</t>
+          <t>510492000001517029</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5050,17 +5050,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>242114</t>
+          <t>242121</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>510492000001378001</t>
+          <t>510492000001517001</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
+          <t>Max Out Tutoring</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>270.0</v>
+        <v>360.0</v>
       </c>
       <c r="N66" t="n">
-        <v>270.0</v>
+        <v>480.0</v>
       </c>
       <c r="O66" t="n">
         <v>1.0</v>
@@ -5081,7 +5081,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>510492000001517029</t>
+          <t>510492000001517056</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5119,17 +5119,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>242121</t>
+          <t>242122</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>510492000001517001</t>
+          <t>510492000001088061</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Max Out Tutoring</t>
+          <t>Drive with Greta</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>360.0</v>
+        <v>28.8</v>
       </c>
       <c r="N67" t="n">
-        <v>480.0</v>
+        <v>28.8</v>
       </c>
       <c r="O67" t="n">
         <v>1.0</v>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>510492000001517056</t>
+          <t>510492000001517086</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5188,17 +5188,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>242122</t>
+          <t>242124</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>510492000001088061</t>
+          <t>510492000001260001</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Drive with Greta</t>
+          <t>Elite Learning Epsom Ltd</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>28.8</v>
+        <v>57.24</v>
       </c>
       <c r="N68" t="n">
-        <v>28.8</v>
+        <v>57.24</v>
       </c>
       <c r="O68" t="n">
         <v>1.0</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>510492000001517086</t>
+          <t>510492000001517128</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5257,17 +5257,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>242124</t>
+          <t>242127</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>510492000001260001</t>
+          <t>510492000001025001</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Elite Learning Epsom Ltd</t>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>57.24</v>
+        <v>125.0</v>
       </c>
       <c r="N69" t="n">
-        <v>57.24</v>
+        <v>375.0</v>
       </c>
       <c r="O69" t="n">
         <v>1.0</v>
@@ -5288,7 +5288,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>510492000001517128</t>
+          <t>510492000001527001</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>242127</t>
+          <t>242128</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>510492000001025001</t>
+          <t>510492000000256001</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+          <t>OPTIMUM GLOBAL LINKS</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>125.0</v>
+        <v>70.0</v>
       </c>
       <c r="N70" t="n">
-        <v>375.0</v>
+        <v>120.0</v>
       </c>
       <c r="O70" t="n">
         <v>1.0</v>
@@ -5357,7 +5357,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>510492000001527001</t>
+          <t>510492000001543036</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5395,17 +5395,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>242128</t>
+          <t>242133</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>510492000000256001</t>
+          <t>510492000001543027</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>OPTIMUM GLOBAL LINKS</t>
+          <t>MRB ELITE PROTECTION &amp; MAINTENANCE LTD</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>70.0</v>
+        <v>420.0</v>
       </c>
       <c r="N71" t="n">
-        <v>120.0</v>
+        <v>420.0</v>
       </c>
       <c r="O71" t="n">
         <v>1.0</v>
@@ -5426,7 +5426,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>510492000001543036</t>
+          <t>510492000001561010</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5464,17 +5464,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>242133</t>
+          <t>242136</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>510492000001543027</t>
+          <t>510492000001561001</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>MRB ELITE PROTECTION &amp; MAINTENANCE LTD</t>
+          <t>BURTON DRIVING SCHOOL LTD</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>420.0</v>
+        <v>300.0</v>
       </c>
       <c r="N72" t="n">
-        <v>420.0</v>
+        <v>300.0</v>
       </c>
       <c r="O72" t="n">
         <v>1.0</v>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>510492000001561010</t>
+          <t>510492000001564010</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5533,17 +5533,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>242136</t>
+          <t>242137</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>510492000001561001</t>
+          <t>510492000001564001</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>BURTON DRIVING SCHOOL LTD</t>
+          <t>Stabilus Safety GmbH</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>300.0</v>
+        <v>780.0</v>
       </c>
       <c r="N73" t="n">
-        <v>300.0</v>
+        <v>780.0</v>
       </c>
       <c r="O73" t="n">
         <v>1.0</v>
@@ -5564,7 +5564,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>510492000001564010</t>
+          <t>510492000001566001</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5602,17 +5602,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>242137</t>
+          <t>242138</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>510492000001564001</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Stabilus Safety GmbH</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5621,10 +5621,10 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>780.0</v>
+        <v>238.8</v>
       </c>
       <c r="N74" t="n">
-        <v>780.0</v>
+        <v>238.8</v>
       </c>
       <c r="O74" t="n">
         <v>1.0</v>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>510492000001566001</t>
+          <t>510492000001566037</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5671,17 +5671,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>242138</t>
+          <t>242140</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>510492000001566037</t>
+          <t>510492000001566055</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5740,17 +5740,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>242140</t>
+          <t>242141</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="N76" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O76" t="n">
         <v>1.0</v>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>510492000001566055</t>
+          <t>510492000001566074</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5809,17 +5809,17 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>242141</t>
+          <t>242142</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="N77" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="O77" t="n">
         <v>1.0</v>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>510492000001566074</t>
+          <t>510492000001566182</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5878,17 +5878,17 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>242142</t>
+          <t>242148</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000505059</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>Chorus Music Therapy &amp; Education</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5897,10 +5897,10 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="N78" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="O78" t="n">
         <v>1.0</v>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>510492000001566182</t>
+          <t>510492000001566380</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5947,17 +5947,17 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>242148</t>
+          <t>242159</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>510492000000505059</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Chorus Music Therapy &amp; Education</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5966,155 +5966,17 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="N79" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="O79" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>510492000001566254</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H80" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>242152</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>510492000000742001</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Adam’s Painting and Decorating</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M80" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="O80" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>510492000001566380</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H81" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>242159</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>510492000000123277</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Patrick Shoes Limited</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M81" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="55" t="inlineStr">
+      <c r="A80" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6123,7 +5985,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A82:O82"/>
+    <mergeCell ref="A80:O80"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_overdue_zoho.xlsx
+++ b/AR_overdue_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O80"/>
+  <dimension ref="A1:O79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 09/10/2026</t>
+As of 14/10/2026</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>368</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>328</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>312</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>312</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>281</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>281</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>281</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>250</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>250</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>247</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>247</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>228</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>222</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>222</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>191</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>191</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>191</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>159</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>510492000001338049</t>
+          <t>510492000001338066</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3256,17 +3256,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>241987</t>
+          <t>241988</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3278,7 +3278,7 @@
         <v>238.8</v>
       </c>
       <c r="N40" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="O40" t="n">
         <v>1.0</v>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>510492000001338066</t>
+          <t>510492000001338242</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3325,17 +3325,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>241988</t>
+          <t>241999</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N41" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O41" t="n">
         <v>1.0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>510492000001338242</t>
+          <t>510492000001338370</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3394,17 +3394,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>241999</t>
+          <t>242007</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000001144276</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Creativa Ltd</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3425,7 +3425,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>510492000001338338</t>
+          <t>510492000001388001</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3463,17 +3463,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>242005</t>
+          <t>242021</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001088061</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>Drive with Greta</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="N43" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="O43" t="n">
         <v>1.0</v>
@@ -3494,7 +3494,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>510492000001338370</t>
+          <t>510492000001391088</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3532,17 +3532,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>242007</t>
+          <t>242026</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>510492000001144276</t>
+          <t>510492000001391079</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Creativa Ltd</t>
+          <t>NGS Plumbing &amp; Heating Ltd</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>240.0</v>
+        <v>75.0</v>
       </c>
       <c r="N44" t="n">
-        <v>240.0</v>
+        <v>75.0</v>
       </c>
       <c r="O44" t="n">
         <v>1.0</v>
@@ -3563,7 +3563,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>510492000001388001</t>
+          <t>510492000001403010</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3583,12 +3583,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>242021</t>
+          <t>242027</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>510492000001088061</t>
+          <t>510492000001403001</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Drive with Greta</t>
+          <t>Malvern Renovation</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>360.0</v>
+        <v>120.0</v>
       </c>
       <c r="N45" t="n">
-        <v>360.0</v>
+        <v>120.0</v>
       </c>
       <c r="O45" t="n">
         <v>1.0</v>
@@ -3632,7 +3632,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>510492000001391088</t>
+          <t>510492000001417033</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3670,17 +3670,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>242026</t>
+          <t>242034</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>510492000001391079</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>NGS Plumbing &amp; Heating Ltd</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>75.0</v>
+        <v>238.8</v>
       </c>
       <c r="N46" t="n">
-        <v>75.0</v>
+        <v>238.8</v>
       </c>
       <c r="O46" t="n">
         <v>1.0</v>
@@ -3701,7 +3701,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>510492000001403010</t>
+          <t>510492000001417049</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3739,17 +3739,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>242027</t>
+          <t>242035</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>510492000001403001</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Malvern Renovation</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>120.0</v>
+        <v>238.8</v>
       </c>
       <c r="N47" t="n">
-        <v>120.0</v>
+        <v>477.6</v>
       </c>
       <c r="O47" t="n">
         <v>1.0</v>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>510492000001417033</t>
+          <t>510492000001417066</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3808,17 +3808,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>242034</t>
+          <t>242036</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>510492000001417049</t>
+          <t>510492000001417242</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3877,17 +3877,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>242035</t>
+          <t>242047</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>477.6</v>
+        <v>240.0</v>
       </c>
       <c r="N49" t="n">
-        <v>477.6</v>
+        <v>240.0</v>
       </c>
       <c r="O49" t="n">
         <v>1.0</v>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>510492000001417066</t>
+          <t>510492000001417338</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3946,17 +3946,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>242036</t>
+          <t>242053</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N50" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O50" t="n">
         <v>1.0</v>
@@ -3977,7 +3977,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>510492000001417242</t>
+          <t>510492000001445029</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4015,17 +4015,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>242047</t>
+          <t>242065</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000001445020</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>BORN FOR IT LTD</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>240.0</v>
+        <v>660.0</v>
       </c>
       <c r="N51" t="n">
-        <v>240.0</v>
+        <v>660.0</v>
       </c>
       <c r="O51" t="n">
         <v>1.0</v>
@@ -4046,7 +4046,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>510492000001417338</t>
+          <t>510492000001460089</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4084,17 +4084,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>242053</t>
+          <t>242075</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000639001</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>De'Osa Engineering Services</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>240.0</v>
+        <v>120.0</v>
       </c>
       <c r="N52" t="n">
-        <v>240.0</v>
+        <v>120.0</v>
       </c>
       <c r="O52" t="n">
         <v>1.0</v>
@@ -4115,7 +4115,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>510492000001445029</t>
+          <t>510492000001460115</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4153,17 +4153,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>242065</t>
+          <t>242076</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>510492000001445020</t>
+          <t>510492000001460106</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>BORN FOR IT LTD</t>
+          <t>MOUNTAINS OF GLORY</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>660.0</v>
+        <v>250.0</v>
       </c>
       <c r="N53" t="n">
-        <v>660.0</v>
+        <v>250.0</v>
       </c>
       <c r="O53" t="n">
         <v>1.0</v>
@@ -4184,7 +4184,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>510492000001359025</t>
+          <t>510492000001460138</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4222,17 +4222,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>242012</t>
+          <t>242077</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>510492000000317525</t>
+          <t>510492000000386033</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>EAGLE PROPERTY CARE</t>
+          <t>ALPHA EUROPE LTD</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4253,7 +4253,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>510492000001460089</t>
+          <t>510492000001359025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>242075</t>
+          <t>242012</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>510492000000639001</t>
+          <t>510492000000317525</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>De'Osa Engineering Services</t>
+          <t>EAGLE PROPERTY CARE</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="N55" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="O55" t="n">
         <v>1.0</v>
@@ -4322,7 +4322,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>510492000001460115</t>
+          <t>510492000001482001</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4360,17 +4360,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>242076</t>
+          <t>242082</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>510492000001460106</t>
+          <t>510492000001057001</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>MOUNTAINS OF GLORY</t>
+          <t>Corby Motors Ltd</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>250.0</v>
+        <v>55.0</v>
       </c>
       <c r="N56" t="n">
-        <v>250.0</v>
+        <v>555.0</v>
       </c>
       <c r="O56" t="n">
         <v>1.0</v>
@@ -4391,7 +4391,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>510492000001460138</t>
+          <t>510492000001482018</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4429,17 +4429,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>242077</t>
+          <t>242083</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>510492000000386033</t>
+          <t>510492000001413024</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>ALPHA EUROPE LTD</t>
+          <t>88 DRIVING SCHOOL LTD</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4448,10 +4448,10 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>240.0</v>
+        <v>110.0</v>
       </c>
       <c r="N57" t="n">
-        <v>240.0</v>
+        <v>110.0</v>
       </c>
       <c r="O57" t="n">
         <v>1.0</v>
@@ -4460,7 +4460,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>510492000001482001</t>
+          <t>510492000001486010</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4498,17 +4498,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>242082</t>
+          <t>242085</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>510492000001057001</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Corby Motors Ltd</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>55.0</v>
+        <v>238.8</v>
       </c>
       <c r="N58" t="n">
-        <v>555.0</v>
+        <v>238.8</v>
       </c>
       <c r="O58" t="n">
         <v>1.0</v>
@@ -4529,7 +4529,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>510492000001482018</t>
+          <t>510492000001486042</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4567,17 +4567,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>242083</t>
+          <t>242087</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>510492000001413024</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>88 DRIVING SCHOOL LTD</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>110.0</v>
+        <v>238.8</v>
       </c>
       <c r="N59" t="n">
-        <v>110.0</v>
+        <v>238.8</v>
       </c>
       <c r="O59" t="n">
         <v>1.0</v>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>510492000001486010</t>
+          <t>510492000001486058</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>242085</t>
+          <t>242088</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="N60" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O60" t="n">
         <v>1.0</v>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>510492000001486042</t>
+          <t>510492000001486075</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4705,17 +4705,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>242087</t>
+          <t>242089</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>510492000001486058</t>
+          <t>510492000001486347</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>242088</t>
+          <t>242106</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>477.6</v>
+        <v>240.0</v>
       </c>
       <c r="N62" t="n">
-        <v>477.6</v>
+        <v>240.0</v>
       </c>
       <c r="O62" t="n">
         <v>1.0</v>
@@ -4805,7 +4805,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>510492000001486075</t>
+          <t>510492000001496109</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4843,17 +4843,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>242089</t>
+          <t>242114</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000001378001</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>238.8</v>
+        <v>270.0</v>
       </c>
       <c r="N63" t="n">
-        <v>238.8</v>
+        <v>270.0</v>
       </c>
       <c r="O63" t="n">
         <v>1.0</v>
@@ -4874,7 +4874,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>510492000001486347</t>
+          <t>510492000001517029</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4912,17 +4912,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>242106</t>
+          <t>242121</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001517001</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>Max Out Tutoring</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="N64" t="n">
-        <v>240.0</v>
+        <v>480.0</v>
       </c>
       <c r="O64" t="n">
         <v>1.0</v>
@@ -4943,7 +4943,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>510492000001496109</t>
+          <t>510492000001517056</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>242114</t>
+          <t>242122</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>510492000001378001</t>
+          <t>510492000001088061</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
+          <t>Drive with Greta</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>270.0</v>
+        <v>28.8</v>
       </c>
       <c r="N65" t="n">
-        <v>270.0</v>
+        <v>28.8</v>
       </c>
       <c r="O65" t="n">
         <v>1.0</v>
@@ -5012,7 +5012,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>510492000001517029</t>
+          <t>510492000001517086</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5050,17 +5050,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>242121</t>
+          <t>242124</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>510492000001517001</t>
+          <t>510492000001260001</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Max Out Tutoring</t>
+          <t>Elite Learning Epsom Ltd</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>360.0</v>
+        <v>57.24</v>
       </c>
       <c r="N66" t="n">
-        <v>480.0</v>
+        <v>57.24</v>
       </c>
       <c r="O66" t="n">
         <v>1.0</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>510492000001517056</t>
+          <t>510492000001517128</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5119,17 +5119,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>242122</t>
+          <t>242127</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>510492000001088061</t>
+          <t>510492000001025001</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Drive with Greta</t>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>28.8</v>
+        <v>125.0</v>
       </c>
       <c r="N67" t="n">
-        <v>28.8</v>
+        <v>375.0</v>
       </c>
       <c r="O67" t="n">
         <v>1.0</v>
@@ -5150,7 +5150,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>510492000001517086</t>
+          <t>510492000001527001</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5188,17 +5188,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>242124</t>
+          <t>242128</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>510492000001260001</t>
+          <t>510492000000256001</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Elite Learning Epsom Ltd</t>
+          <t>OPTIMUM GLOBAL LINKS</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>57.24</v>
+        <v>70.0</v>
       </c>
       <c r="N68" t="n">
-        <v>57.24</v>
+        <v>120.0</v>
       </c>
       <c r="O68" t="n">
         <v>1.0</v>
@@ -5219,7 +5219,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>510492000001517128</t>
+          <t>510492000001543036</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5257,17 +5257,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>242127</t>
+          <t>242133</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>510492000001025001</t>
+          <t>510492000001543027</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+          <t>MRB ELITE PROTECTION &amp; MAINTENANCE LTD</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>125.0</v>
+        <v>420.0</v>
       </c>
       <c r="N69" t="n">
-        <v>375.0</v>
+        <v>420.0</v>
       </c>
       <c r="O69" t="n">
         <v>1.0</v>
@@ -5288,7 +5288,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>510492000001527001</t>
+          <t>510492000001564010</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>242128</t>
+          <t>242137</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>510492000000256001</t>
+          <t>510492000001564001</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>OPTIMUM GLOBAL LINKS</t>
+          <t>Stabilus Safety GmbH</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>70.0</v>
+        <v>780.0</v>
       </c>
       <c r="N70" t="n">
-        <v>120.0</v>
+        <v>780.0</v>
       </c>
       <c r="O70" t="n">
         <v>1.0</v>
@@ -5357,7 +5357,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>510492000001543036</t>
+          <t>510492000001566001</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5395,17 +5395,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>242133</t>
+          <t>242138</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>510492000001543027</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>MRB ELITE PROTECTION &amp; MAINTENANCE LTD</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>420.0</v>
+        <v>238.8</v>
       </c>
       <c r="N71" t="n">
-        <v>420.0</v>
+        <v>238.8</v>
       </c>
       <c r="O71" t="n">
         <v>1.0</v>
@@ -5426,7 +5426,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>510492000001561010</t>
+          <t>510492000001566037</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5464,17 +5464,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>242136</t>
+          <t>242140</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>510492000001561001</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>BURTON DRIVING SCHOOL LTD</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>300.0</v>
+        <v>238.8</v>
       </c>
       <c r="N72" t="n">
-        <v>300.0</v>
+        <v>238.8</v>
       </c>
       <c r="O72" t="n">
         <v>1.0</v>
@@ -5495,7 +5495,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>510492000001564010</t>
+          <t>510492000001566055</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5533,17 +5533,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>242137</t>
+          <t>242141</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>510492000001564001</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Stabilus Safety GmbH</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>780.0</v>
+        <v>477.6</v>
       </c>
       <c r="N73" t="n">
-        <v>780.0</v>
+        <v>477.6</v>
       </c>
       <c r="O73" t="n">
         <v>1.0</v>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>510492000001566001</t>
+          <t>510492000001566074</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5602,17 +5602,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>242138</t>
+          <t>242142</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>510492000001566037</t>
+          <t>510492000001566182</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5671,17 +5671,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>242140</t>
+          <t>242148</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000505059</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>Chorus Music Therapy &amp; Education</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5690,10 +5690,10 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="N75" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="O75" t="n">
         <v>1.0</v>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>510492000001566055</t>
+          <t>510492000001566380</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>242141</t>
+          <t>242159</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>477.6</v>
+        <v>240.0</v>
       </c>
       <c r="N76" t="n">
-        <v>477.6</v>
+        <v>240.0</v>
       </c>
       <c r="O76" t="n">
         <v>1.0</v>
@@ -5771,7 +5771,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>510492000001566074</t>
+          <t>510492000001582047</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5809,17 +5809,17 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>242142</t>
+          <t>242168</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000001582038</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>CONNECT DRIVING SCHOOL LIMITED</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>238.8</v>
+        <v>370.0</v>
       </c>
       <c r="N77" t="n">
-        <v>238.8</v>
+        <v>620.0</v>
       </c>
       <c r="O77" t="n">
         <v>1.0</v>
@@ -5840,7 +5840,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>510492000001566182</t>
+          <t>510492000001587077</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5878,17 +5878,17 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>242148</t>
+          <t>242170</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>510492000000505059</t>
+          <t>510492000001025001</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Chorus Music Therapy &amp; Education</t>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5897,86 +5897,17 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>120.0</v>
+        <v>354.0</v>
       </c>
       <c r="N78" t="n">
-        <v>120.0</v>
+        <v>354.0</v>
       </c>
       <c r="O78" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>510492000001566380</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H79" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>242159</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>510492000000123277</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Patrick Shoes Limited</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M79" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="O79" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="55" t="inlineStr">
+      <c r="A79" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5985,7 +5916,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A80:O80"/>
+    <mergeCell ref="A79:O79"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_overdue_zoho.xlsx
+++ b/AR_overdue_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O79"/>
+  <dimension ref="A1:O76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 14/10/2026</t>
+As of 28/10/2026</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>382</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>342</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>326</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>326</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>295</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>295</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>295</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>264</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>264</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>261</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>261</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>248</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>242</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>236</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>236</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>224</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>203</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>175</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>175</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>173</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>175</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>175</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>144</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>144</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>144</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>144</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>126</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3425,7 +3425,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>510492000001388001</t>
+          <t>510492000001359025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3463,17 +3463,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>242021</t>
+          <t>242012</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>510492000001088061</t>
+          <t>510492000000317525</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Drive with Greta</t>
+          <t>EAGLE PROPERTY CARE</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>360.0</v>
+        <v>240.0</v>
       </c>
       <c r="N43" t="n">
-        <v>360.0</v>
+        <v>240.0</v>
       </c>
       <c r="O43" t="n">
         <v>1.0</v>
@@ -3494,7 +3494,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>510492000001391088</t>
+          <t>510492000001388001</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3532,17 +3532,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>242026</t>
+          <t>242021</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>510492000001391079</t>
+          <t>510492000001088061</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>NGS Plumbing &amp; Heating Ltd</t>
+          <t>Drive with Greta</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>75.0</v>
+        <v>360.0</v>
       </c>
       <c r="N44" t="n">
-        <v>75.0</v>
+        <v>360.0</v>
       </c>
       <c r="O44" t="n">
         <v>1.0</v>
@@ -3563,34 +3563,34 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>510492000001391088</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>510492000001403010</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t/>
@@ -3601,17 +3601,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>242027</t>
+          <t>242026</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>510492000001403001</t>
+          <t>510492000001391079</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Malvern Renovation</t>
+          <t>NGS Plumbing &amp; Heating Ltd</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>120.0</v>
+        <v>75.0</v>
       </c>
       <c r="N45" t="n">
-        <v>120.0</v>
+        <v>75.0</v>
       </c>
       <c r="O45" t="n">
         <v>1.0</v>
@@ -3632,7 +3632,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>510492000001417033</t>
+          <t>510492000001403010</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3670,17 +3670,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>242034</t>
+          <t>242027</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000001403001</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>Malvern Renovation</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="N46" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="O46" t="n">
         <v>1.0</v>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>510492000001417049</t>
+          <t>510492000001417033</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3739,17 +3739,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>242035</t>
+          <t>242034</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3761,7 +3761,7 @@
         <v>238.8</v>
       </c>
       <c r="N47" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="O47" t="n">
         <v>1.0</v>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3908,7 +3908,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>510492000001417338</t>
+          <t>510492000001445029</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3946,17 +3946,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>242053</t>
+          <t>242065</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001445020</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>BORN FOR IT LTD</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>240.0</v>
+        <v>660.0</v>
       </c>
       <c r="N50" t="n">
-        <v>240.0</v>
+        <v>660.0</v>
       </c>
       <c r="O50" t="n">
         <v>1.0</v>
@@ -3977,7 +3977,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>510492000001445029</t>
+          <t>510492000001460089</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4015,17 +4015,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>242065</t>
+          <t>242075</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>510492000001445020</t>
+          <t>510492000000639001</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>BORN FOR IT LTD</t>
+          <t>De'Osa Engineering Services</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>660.0</v>
+        <v>120.0</v>
       </c>
       <c r="N51" t="n">
-        <v>660.0</v>
+        <v>120.0</v>
       </c>
       <c r="O51" t="n">
         <v>1.0</v>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>510492000001460089</t>
+          <t>510492000001460115</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4084,17 +4084,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>242075</t>
+          <t>242076</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>510492000000639001</t>
+          <t>510492000001460106</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>De'Osa Engineering Services</t>
+          <t>MOUNTAINS OF GLORY</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>120.0</v>
+        <v>250.0</v>
       </c>
       <c r="N52" t="n">
-        <v>120.0</v>
+        <v>250.0</v>
       </c>
       <c r="O52" t="n">
         <v>1.0</v>
@@ -4115,7 +4115,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>510492000001460115</t>
+          <t>510492000001460138</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4153,17 +4153,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>242076</t>
+          <t>242077</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>510492000001460106</t>
+          <t>510492000000386033</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>MOUNTAINS OF GLORY</t>
+          <t>ALPHA EUROPE LTD</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>250.0</v>
+        <v>240.0</v>
       </c>
       <c r="N53" t="n">
-        <v>250.0</v>
+        <v>240.0</v>
       </c>
       <c r="O53" t="n">
         <v>1.0</v>
@@ -4184,7 +4184,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>510492000001460138</t>
+          <t>510492000001482001</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4222,17 +4222,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>242077</t>
+          <t>242082</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>510492000000386033</t>
+          <t>510492000001057001</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>ALPHA EUROPE LTD</t>
+          <t>Corby Motors Ltd</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>240.0</v>
+        <v>55.0</v>
       </c>
       <c r="N54" t="n">
-        <v>240.0</v>
+        <v>555.0</v>
       </c>
       <c r="O54" t="n">
         <v>1.0</v>
@@ -4253,7 +4253,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>510492000001359025</t>
+          <t>510492000001482018</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>242012</t>
+          <t>242083</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>510492000000317525</t>
+          <t>510492000001413024</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>EAGLE PROPERTY CARE</t>
+          <t>88 DRIVING SCHOOL LTD</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>240.0</v>
+        <v>110.0</v>
       </c>
       <c r="N55" t="n">
-        <v>240.0</v>
+        <v>110.0</v>
       </c>
       <c r="O55" t="n">
         <v>1.0</v>
@@ -4322,7 +4322,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>510492000001482001</t>
+          <t>510492000001486010</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4360,17 +4360,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>242082</t>
+          <t>242085</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>510492000001057001</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Corby Motors Ltd</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>55.0</v>
+        <v>238.8</v>
       </c>
       <c r="N56" t="n">
-        <v>555.0</v>
+        <v>238.8</v>
       </c>
       <c r="O56" t="n">
         <v>1.0</v>
@@ -4391,7 +4391,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>510492000001482018</t>
+          <t>510492000001486042</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4429,17 +4429,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>242083</t>
+          <t>242087</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>510492000001413024</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>88 DRIVING SCHOOL LTD</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4448,10 +4448,10 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>110.0</v>
+        <v>238.8</v>
       </c>
       <c r="N57" t="n">
-        <v>110.0</v>
+        <v>238.8</v>
       </c>
       <c r="O57" t="n">
         <v>1.0</v>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>510492000001486010</t>
+          <t>510492000001486058</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4498,17 +4498,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>242085</t>
+          <t>242088</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4520,7 +4520,7 @@
         <v>238.8</v>
       </c>
       <c r="N58" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O58" t="n">
         <v>1.0</v>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>510492000001486042</t>
+          <t>510492000001486075</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4567,17 +4567,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>242087</t>
+          <t>242089</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>510492000001486058</t>
+          <t>510492000001486347</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>242088</t>
+          <t>242106</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>477.6</v>
+        <v>240.0</v>
       </c>
       <c r="N60" t="n">
-        <v>477.6</v>
+        <v>240.0</v>
       </c>
       <c r="O60" t="n">
         <v>1.0</v>
@@ -4667,7 +4667,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>510492000001486075</t>
+          <t>510492000001496109</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4705,17 +4705,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>242089</t>
+          <t>242114</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000001378001</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>238.8</v>
+        <v>270.0</v>
       </c>
       <c r="N61" t="n">
-        <v>238.8</v>
+        <v>270.0</v>
       </c>
       <c r="O61" t="n">
         <v>1.0</v>
@@ -4736,7 +4736,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>510492000001486347</t>
+          <t>510492000001517029</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4774,17 +4774,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>242106</t>
+          <t>242121</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001517001</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>Max Out Tutoring</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="N62" t="n">
-        <v>240.0</v>
+        <v>480.0</v>
       </c>
       <c r="O62" t="n">
         <v>1.0</v>
@@ -4805,7 +4805,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>510492000001496109</t>
+          <t>510492000001517056</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4843,17 +4843,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>242114</t>
+          <t>242122</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>510492000001378001</t>
+          <t>510492000001088061</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>ALTAI MOUNTAIN SHILAJIT LTD</t>
+          <t>Drive with Greta</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>270.0</v>
+        <v>28.8</v>
       </c>
       <c r="N63" t="n">
-        <v>270.0</v>
+        <v>28.8</v>
       </c>
       <c r="O63" t="n">
         <v>1.0</v>
@@ -4874,7 +4874,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>510492000001517029</t>
+          <t>510492000001517086</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4912,17 +4912,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>242121</t>
+          <t>242124</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>510492000001517001</t>
+          <t>510492000001260001</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Max Out Tutoring</t>
+          <t>Elite Learning Epsom Ltd</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>360.0</v>
+        <v>57.24</v>
       </c>
       <c r="N64" t="n">
-        <v>480.0</v>
+        <v>57.24</v>
       </c>
       <c r="O64" t="n">
         <v>1.0</v>
@@ -4943,7 +4943,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>510492000001517056</t>
+          <t>510492000001527001</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>242122</t>
+          <t>242128</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>510492000001088061</t>
+          <t>510492000000256001</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Drive with Greta</t>
+          <t>OPTIMUM GLOBAL LINKS</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>28.8</v>
+        <v>70.0</v>
       </c>
       <c r="N65" t="n">
-        <v>28.8</v>
+        <v>120.0</v>
       </c>
       <c r="O65" t="n">
         <v>1.0</v>
@@ -5012,7 +5012,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>510492000001517086</t>
+          <t>510492000001543036</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5050,17 +5050,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>242124</t>
+          <t>242133</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>510492000001260001</t>
+          <t>510492000001543027</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Elite Learning Epsom Ltd</t>
+          <t>MRB ELITE PROTECTION &amp; MAINTENANCE LTD</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>57.24</v>
+        <v>420.0</v>
       </c>
       <c r="N66" t="n">
-        <v>57.24</v>
+        <v>420.0</v>
       </c>
       <c r="O66" t="n">
         <v>1.0</v>
@@ -5081,7 +5081,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>510492000001517128</t>
+          <t>510492000001566001</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5119,17 +5119,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>242127</t>
+          <t>242138</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>510492000001025001</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>125.0</v>
+        <v>238.8</v>
       </c>
       <c r="N67" t="n">
-        <v>375.0</v>
+        <v>238.8</v>
       </c>
       <c r="O67" t="n">
         <v>1.0</v>
@@ -5150,7 +5150,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>510492000001527001</t>
+          <t>510492000001566037</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5188,17 +5188,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>242128</t>
+          <t>242140</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>510492000000256001</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>OPTIMUM GLOBAL LINKS</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>70.0</v>
+        <v>238.8</v>
       </c>
       <c r="N68" t="n">
-        <v>120.0</v>
+        <v>238.8</v>
       </c>
       <c r="O68" t="n">
         <v>1.0</v>
@@ -5219,7 +5219,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>510492000001543036</t>
+          <t>510492000001566055</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5257,17 +5257,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>242133</t>
+          <t>242141</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>510492000001543027</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>MRB ELITE PROTECTION &amp; MAINTENANCE LTD</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>420.0</v>
+        <v>477.6</v>
       </c>
       <c r="N69" t="n">
-        <v>420.0</v>
+        <v>477.6</v>
       </c>
       <c r="O69" t="n">
         <v>1.0</v>
@@ -5288,7 +5288,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>510492000001564010</t>
+          <t>510492000001566074</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>242137</t>
+          <t>242142</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>510492000001564001</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Stabilus Safety GmbH</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>780.0</v>
+        <v>238.8</v>
       </c>
       <c r="N70" t="n">
-        <v>780.0</v>
+        <v>238.8</v>
       </c>
       <c r="O70" t="n">
         <v>1.0</v>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>510492000001566001</t>
+          <t>510492000001566182</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5395,17 +5395,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>242138</t>
+          <t>242148</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000505059</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>Chorus Music Therapy &amp; Education</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="N71" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="O71" t="n">
         <v>1.0</v>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>510492000001566037</t>
+          <t>510492000001566380</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5464,17 +5464,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>242140</t>
+          <t>242159</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N72" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O72" t="n">
         <v>1.0</v>
@@ -5495,7 +5495,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>510492000001566055</t>
+          <t>510492000001587077</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5533,17 +5533,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>242141</t>
+          <t>242170</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001025001</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>477.6</v>
+        <v>354.0</v>
       </c>
       <c r="N73" t="n">
-        <v>477.6</v>
+        <v>354.0</v>
       </c>
       <c r="O73" t="n">
         <v>1.0</v>
@@ -5564,7 +5564,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>510492000001566074</t>
+          <t>510492000001591001</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5602,17 +5602,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>242142</t>
+          <t>242171</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5621,10 +5621,10 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>238.8</v>
+        <v>132.0</v>
       </c>
       <c r="N74" t="n">
-        <v>238.8</v>
+        <v>132.0</v>
       </c>
       <c r="O74" t="n">
         <v>1.0</v>
@@ -5633,7 +5633,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>510492000001566182</t>
+          <t>510492000001610010</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5671,17 +5671,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>242148</t>
+          <t>242172</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>510492000000505059</t>
+          <t>510492000001610001</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Chorus Music Therapy &amp; Education</t>
+          <t>UK Admission Manchester</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5690,224 +5690,17 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="N75" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="O75" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>510492000001566380</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H76" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>242159</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>510492000000123277</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Patrick Shoes Limited</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M76" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="N76" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>510492000001582047</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H77" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>242168</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>510492000001582038</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>CONNECT DRIVING SCHOOL LIMITED</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M77" t="n">
-        <v>370.0</v>
-      </c>
-      <c r="N77" t="n">
-        <v>620.0</v>
-      </c>
-      <c r="O77" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>510492000001587077</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H78" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>242170</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>510492000001025001</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M78" t="n">
-        <v>354.0</v>
-      </c>
-      <c r="N78" t="n">
-        <v>354.0</v>
-      </c>
-      <c r="O78" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="55" t="inlineStr">
+      <c r="A76" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5916,7 +5709,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A79:O79"/>
+    <mergeCell ref="A76:O76"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_overdue_zoho.xlsx
+++ b/AR_overdue_zoho.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -48,6 +48,11 @@
       <color rgb="FF000000"/>
       <b val="true"/>
       <i val="true"/>
+    </font>
+    <font>
+      <name val="arial"/>
+      <sz val="10.0"/>
+      <color rgb="FF666666"/>
     </font>
     <font>
       <name val="arial"/>
@@ -93,6 +98,11 @@
       <color rgb="FF000000"/>
       <b val="true"/>
       <i val="true"/>
+    </font>
+    <font>
+      <name val="arial"/>
+      <sz val="10.0"/>
+      <color rgb="FF666666"/>
     </font>
     <font>
       <name val="arial"/>
@@ -293,7 +303,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
@@ -301,253 +311,271 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -577,11 +605,11 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" ht="70.0">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 28/10/2026</t>
+As of 31/10/2026</t>
         </is>
       </c>
     </row>
@@ -685,7 +713,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>385</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -754,7 +782,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>345</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -823,7 +851,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>329</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -892,7 +920,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>329</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -961,7 +989,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>298</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1030,7 +1058,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>298</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1099,7 +1127,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>298</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1168,7 +1196,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>267</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1237,7 +1265,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>267</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1306,7 +1334,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>264</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1375,7 +1403,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>264</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1444,7 +1472,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>251</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1513,7 +1541,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>245</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1582,7 +1610,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>239</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1651,7 +1679,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>239</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1720,7 +1748,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>237</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1789,7 +1817,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>237</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1858,7 +1886,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>237</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1927,7 +1955,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>237</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1996,7 +2024,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>227</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2065,7 +2093,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>208</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2134,7 +2162,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>208</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2203,7 +2231,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2272,7 +2300,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>208</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2341,7 +2369,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2410,7 +2438,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2479,7 +2507,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2548,7 +2576,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2617,7 +2645,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2686,7 +2714,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2755,7 +2783,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2824,7 +2852,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2893,7 +2921,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2962,7 +2990,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3031,7 +3059,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3100,7 +3128,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3169,7 +3197,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>117</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3238,7 +3266,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>117</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3307,7 +3335,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>117</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3376,7 +3404,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>117</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3445,7 +3473,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3514,7 +3542,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3583,7 +3611,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3652,7 +3680,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3721,7 +3749,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>86</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3790,7 +3818,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>86</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3859,7 +3887,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>86</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3928,7 +3956,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3997,7 +4025,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4066,7 +4094,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4135,7 +4163,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4204,7 +4232,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4273,7 +4301,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4342,7 +4370,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4411,7 +4439,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4480,7 +4508,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4549,7 +4577,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4618,7 +4646,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4687,7 +4715,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4756,7 +4784,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4825,7 +4853,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4894,7 +4922,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4963,7 +4991,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5032,7 +5060,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5101,7 +5129,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5170,7 +5198,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5239,7 +5267,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5308,7 +5336,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5377,7 +5405,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5446,7 +5474,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5495,7 +5523,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5505,7 +5533,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>510492000001587077</t>
+          <t>510492000001591001</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5515,12 +5543,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5533,17 +5561,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>242170</t>
+          <t>242171</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>510492000001025001</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5552,10 +5580,10 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>354.0</v>
+        <v>132.0</v>
       </c>
       <c r="N73" t="n">
-        <v>354.0</v>
+        <v>132.0</v>
       </c>
       <c r="O73" t="n">
         <v>1.0</v>
@@ -5564,7 +5592,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5574,7 +5602,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>510492000001591001</t>
+          <t>510492000001617001</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5584,12 +5612,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5602,17 +5630,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>242171</t>
+          <t>242175</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000001582038</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>CONNECT DRIVING SCHOOL LIMITED</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5621,10 +5649,10 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>132.0</v>
+        <v>480.0</v>
       </c>
       <c r="N74" t="n">
-        <v>132.0</v>
+        <v>480.0</v>
       </c>
       <c r="O74" t="n">
         <v>1.0</v>
@@ -5633,7 +5661,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5643,7 +5671,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>510492000001610010</t>
+          <t>510492000001617021</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5658,7 +5686,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5671,17 +5699,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>242172</t>
+          <t>242176</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>510492000001610001</t>
+          <t>510492000001517001</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>UK Admission Manchester</t>
+          <t>Max Out Tutoring</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5690,17 +5718,17 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="N75" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="O75" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="55" t="inlineStr">
+      <c r="A76" s="59" t="inlineStr">
         <is>
           <t/>
         </is>
